--- a/КАТАЛОГ-ТАБЛИЦА.xlsx
+++ b/КАТАЛОГ-ТАБЛИЦА.xlsx
@@ -9,9 +9,11 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Каталог" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Плитка" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Каталог'!$A$1:$Q$275</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Плитка'!$A$1:$J$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -99,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -114,6 +116,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -18976,4 +18979,8751 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J175"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Форма</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Название на сайте</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Тип окраски</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Цена ₽/м²</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Высота</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Поддон</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Морозостойкость</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Фото</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Поставщик (на сайт НЕ выводим)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>tile-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Агат коричневый</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>tile-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Агат коричневый — Мрамор</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="n">
+        <v>1060</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>tile-003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Агат кофейный</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>tile-004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Агат оранжевый</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>tile-005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Агат серокофейный</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>tile-006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Агат солнечный</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>tile-007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Антрацит</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>tile-008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Гончар</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>tile-009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Джафар</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>tile-010</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Дюна</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>1010</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>tile-011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Инь и Ян</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>tile-012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Инь и Ян — Мрамор</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>1060</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>tile-013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Клинкер</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>tile-014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Кофе с молоком</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>tile-015</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Моно 1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>650</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>tile-016</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Моно 2</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>710</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>tile-017</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Моно 3</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>760</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>tile-018</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Моно 4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>760</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>tile-019</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Моно 5</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>710</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>tile-020</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Моно 6</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>710</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>tile-021</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Моно 7</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>710</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>tile-022</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Моно 8</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>760</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>tile-023</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Светлый листопад</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>tile-024</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Солнечный Инь и Ян</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>tile-025</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Степь</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>tile-026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Темный листопад</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>tile-027</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Хаски</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>tile-028</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Хаски — Мрамор</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>1060</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>tile-029</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Новый город</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Яшма</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>tile-030</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Старый город</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Агат коричневый</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>tile-031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Старый город</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Агат кофейный — Мрамор</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>1060</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>tile-032</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Старый город</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Агат оранжевый</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>tile-033</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Старый город</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Агат солнечный</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>tile-034</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Старый город</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Антрацит</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>tile-035</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Старый город</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Гончар</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>tile-036</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Старый город</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Джафар</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>tile-037</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Старый город</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Дюна</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>1010</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>tile-038</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Старый город</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Инь и Ян</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>tile-039</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Старый город</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Клинкер</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>tile-040</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Старый город</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Кофе с молоком</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>tile-041</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Старый город</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Моно 1</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>650</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>tile-042</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Старый город</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Моно 2</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>710</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>tile-043</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Старый город</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Моно 3</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>760</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>tile-044</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Старый город</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Моно 4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>760</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>tile-045</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Старый город</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Моно 5</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>710</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>tile-046</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Старый город</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Моно 6</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>710</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>tile-047</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Старый город</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Моно 7</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="n">
+        <v>710</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>tile-048</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Старый город</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Моно 8</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="n">
+        <v>760</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>tile-049</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Старый город</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Светлый листопад гладкий</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>tile-050</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Старый город</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Степь</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>tile-051</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Старый город</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Тёмный листопад</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>tile-052</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Старый город</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Хаски</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>tile-053</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Старый город</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Яшма</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>tile-054</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Брусчатка</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Агат коричневый</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>tile-055</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Брусчатка</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Агат кофейный</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>tile-056</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Брусчатка</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Агат оранжевый</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>tile-057</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Брусчатка</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Агат солнечный</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>tile-058</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Брусчатка</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Антрацит</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>tile-059</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Брусчатка</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Гончар</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E60" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>tile-060</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Брусчатка</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Джафар</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>tile-061</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Брусчатка</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Дюна</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E62" s="12" t="n">
+        <v>1010</v>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>tile-062</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Брусчатка</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Клинкер</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>tile-063</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Брусчатка</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Кофе с молоком</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E64" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>tile-064</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Брусчатка</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Моно 1</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="n">
+        <v>650</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>tile-065</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Брусчатка</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Моно 2</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E66" s="12" t="n">
+        <v>710</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>tile-066</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Брусчатка</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Моно 3</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="n">
+        <v>760</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>tile-067</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Брусчатка</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Моно 4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="n">
+        <v>760</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>tile-068</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Брусчатка</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Моно 5</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="n">
+        <v>710</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>tile-069</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Брусчатка</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Моно 6</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="n">
+        <v>710</v>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>tile-070</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Брусчатка</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Моно 7</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="n">
+        <v>710</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>tile-071</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Брусчатка</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Моно 8</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="n">
+        <v>760</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>tile-072</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Брусчатка</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Светлый листопад</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>tile-073</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Брусчатка</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Степь</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>tile-074</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Брусчатка</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Темный листопад</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>tile-075</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Брусчатка</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Хаски</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E76" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>tile-076</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Брусчатка</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Яшма</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>tile-077</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Прямоугольник</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Агат коричневый</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>tile-078</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Прямоугольник</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Агат кофейный</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>tile-079</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Прямоугольник</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Агат оранжевый</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>tile-080</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Прямоугольник</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Агат солнечный</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>tile-081</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Прямоугольник</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Антрацит</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>tile-082</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Прямоугольник</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Гончар</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>tile-083</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Прямоугольник</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Джафар</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>tile-084</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Прямоугольник</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Дюна</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="n">
+        <v>1010</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>tile-085</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Прямоугольник</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Инь и Ян</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>tile-086</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Прямоугольник</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Клинкер</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>tile-087</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Прямоугольник</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Кофе с молоком</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>tile-088</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Прямоугольник</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Моно 1</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="n">
+        <v>650</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>tile-089</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Прямоугольник</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Моно 2</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E90" s="12" t="n">
+        <v>710</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>tile-090</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Прямоугольник</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Моно 3</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="n">
+        <v>760</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>tile-091</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Прямоугольник</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Моно 4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="n">
+        <v>760</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>tile-092</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Прямоугольник</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Моно 5</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="n">
+        <v>710</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>tile-093</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Прямоугольник</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Моно 6</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="n">
+        <v>710</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>tile-094</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Прямоугольник</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Моно 7</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="n">
+        <v>710</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>tile-095</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Прямоугольник</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Моно 8</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="n">
+        <v>760</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>tile-096</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Прямоугольник</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Светлый листопад</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>tile-097</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Прямоугольник</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Степь</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E98" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>tile-098</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Прямоугольник</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Тёмный листопад</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>tile-099</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Прямоугольник</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Хаски</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>tile-100</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Прямоугольник</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Яшма</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>tile-101</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Мюнхен</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Агат коричневый</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>tile-102</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Мюнхен</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Агат кофейный</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>tile-103</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Мюнхен</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Агат оранжевый</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>tile-104</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Мюнхен</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Агат солнечный</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>tile-105</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Мюнхен</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Антрацит</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E106" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>tile-106</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Мюнхен</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Гончар</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>tile-107</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Мюнхен</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Джафар</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>tile-108</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Мюнхен</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Дюна</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="n">
+        <v>1060</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>tile-109</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Мюнхен</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Инь и Ян</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E110" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>tile-110</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Мюнхен</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Клинкер</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>tile-111</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Мюнхен</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Кофе с молоком</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E112" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>tile-112</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Мюнхен</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Моно 1</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="n">
+        <v>700</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>tile-113</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Мюнхен</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Моно 2</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E114" s="12" t="n">
+        <v>760</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>tile-114</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Мюнхен</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Моно 3</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="n">
+        <v>810</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>tile-115</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Мюнхен</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Моно 4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E116" s="12" t="n">
+        <v>810</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>tile-116</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Мюнхен</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Моно 5</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="n">
+        <v>760</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>tile-117</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Мюнхен</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Моно 6</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E118" s="12" t="n">
+        <v>760</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>tile-118</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Мюнхен</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Моно 7</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="n">
+        <v>760</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>tile-119</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Мюнхен</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Моно 8</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E120" s="12" t="n">
+        <v>810</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>tile-120</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Мюнхен</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Светлый листопад</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>tile-121</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Мюнхен</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Степь</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>tile-122</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Мюнхен</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Тёмный листопад</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>tile-123</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Мюнхен</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Хаски</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>tile-124</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Мюнхен</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Яшма</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>tile-125</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Паркет</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Агат коричневый</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E126" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>tile-126</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Паркет</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Агат кофейный</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E127" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>tile-127</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Паркет</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Агат оранжевый</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E128" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>tile-128</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Паркет</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Агат солнечный</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E129" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>tile-129</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Паркет</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Антрацит</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E130" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>tile-130</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Паркет</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Гончар</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>tile-131</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Паркет</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Джафар</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E132" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>tile-132</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Паркет</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Дюна</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E133" s="12" t="n">
+        <v>1060</v>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>tile-133</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Паркет</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Инь и Ян</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E134" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>tile-134</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Паркет</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Клинкер</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E135" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>tile-135</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Паркет</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Кофе с молоком</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E136" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>tile-136</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Паркет</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Моно 1</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E137" s="12" t="n">
+        <v>700</v>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>tile-137</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Паркет</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Моно 2</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E138" s="12" t="n">
+        <v>760</v>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>tile-138</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Паркет</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Моно 3</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E139" s="12" t="n">
+        <v>810</v>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>tile-139</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Паркет</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Моно 4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E140" s="12" t="n">
+        <v>810</v>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>tile-140</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Паркет</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Моно 5</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E141" s="12" t="n">
+        <v>760</v>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>tile-141</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Паркет</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Моно 6</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E142" s="12" t="n">
+        <v>760</v>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>tile-142</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Паркет</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Моно 7</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E143" s="12" t="n">
+        <v>760</v>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>tile-143</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Паркет</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Моно 8</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E144" s="12" t="n">
+        <v>810</v>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>tile-144</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Паркет</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Светлый листопад</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E145" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>tile-145</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Паркет</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Степь</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E146" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>tile-146</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Паркет</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Темный листопад</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E147" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>tile-147</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Паркет</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Хаски</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E148" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>tile-148</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Паркет</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Яшма</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E149" s="12" t="n">
+        <v>960</v>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>tile-149</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Асгард</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Агат коричневый</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E150" s="12" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>tile-150</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Асгард</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Агат кофейный</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E151" s="12" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>tile-151</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Асгард</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Агат оранжевый</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E152" s="12" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>tile-152</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Асгард</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Агат солнечный</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E153" s="12" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>tile-153</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Асгард</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Антрацит</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E154" s="12" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>tile-154</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Асгард</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Гончар</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E155" s="12" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>tile-155</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Асгард</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Джафар</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E156" s="12" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>tile-156</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Асгард</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Дюна</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E157" s="12" t="n">
+        <v>1360</v>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>tile-157</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Асгард</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Инь и Ян</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E158" s="12" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>tile-158</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Асгард</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Клинкер</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E159" s="12" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>tile-159</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Асгард</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Кофе с молоком</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E160" s="12" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>tile-160</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Асгард</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Моно 1</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E161" s="12" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>tile-161</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Асгард</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Моно 2</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E162" s="12" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>tile-162</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Асгард</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Моно 3</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E163" s="12" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>tile-163</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Асгард</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Моно 4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E164" s="12" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>tile-164</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Асгард</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Моно 5</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E165" s="12" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>tile-165</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Асгард</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Моно 6</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E166" s="12" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>tile-166</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Асгард</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Моно 7</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>однотонная</t>
+        </is>
+      </c>
+      <c r="E167" s="12" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>tile-167</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Асгард</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Оранжевый</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E168" s="12" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>tile-168</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Асгард</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Светлый листопад</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E169" s="12" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>tile-169</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Асгард</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Степь</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E170" s="12" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>tile-170</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Асгард</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Тёмный листопад</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E171" s="12" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>tile-171</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Асгард</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Хаски</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E172" s="12" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>tile-172</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Асгард</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Яшма</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>колормикс</t>
+        </is>
+      </c>
+      <c r="E173" s="12" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>40мм</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>15 м²</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>bordur-1</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Бордюры</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Бордюр дорожный</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr"/>
+      <c r="E174" s="12" t="n">
+        <v>560</v>
+      </c>
+      <c r="F174" s="2" t="inlineStr"/>
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr"/>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>bordur-2</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Бордюры</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Бордюр садовый</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr"/>
+      <c r="E175" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="F175" s="2" t="inlineStr"/>
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr"/>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>Легион</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J175"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/КАТАЛОГ-ТАБЛИЦА.xlsx
+++ b/КАТАЛОГ-ТАБЛИЦА.xlsx
@@ -19143,9 +19143,9 @@
           <t>F200</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -19293,9 +19293,9 @@
           <t>F200</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -19593,9 +19593,9 @@
           <t>F200</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -20243,9 +20243,9 @@
           <t>F200</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -20317,7 +20317,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Темный листопад</t>
+          <t>Тёмный листопад</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -20443,9 +20443,9 @@
           <t>F200</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -22717,7 +22717,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Темный листопад</t>
+          <t>Тёмный листопад</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -26317,7 +26317,7 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Темный листопад</t>
+          <t>Тёмный листопад</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">

--- a/КАТАЛОГ-ТАБЛИЦА.xlsx
+++ b/КАТАЛОГ-ТАБЛИЦА.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Плитка" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Каталог'!$A$1:$Q$257</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Каталог'!$A$1:$Q$285</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Плитка'!$A$1:$J$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q257"/>
+  <dimension ref="A1:Q285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3954,7 +3954,7 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="n"/>
       <c r="M55" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr"/>
@@ -4019,7 +4019,7 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="n"/>
       <c r="M56" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr"/>
@@ -4084,7 +4084,7 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="n"/>
       <c r="M57" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr"/>
@@ -4149,7 +4149,7 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="n"/>
       <c r="M58" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr"/>
@@ -4214,7 +4214,7 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="n"/>
       <c r="M59" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr"/>
@@ -4279,7 +4279,7 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="n"/>
       <c r="M60" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr"/>
@@ -4344,7 +4344,7 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="n"/>
       <c r="M61" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr"/>
@@ -4409,7 +4409,7 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="n"/>
       <c r="M62" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr"/>
@@ -4474,7 +4474,7 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="n"/>
       <c r="M63" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr"/>
@@ -4539,7 +4539,7 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="n"/>
       <c r="M64" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr"/>
@@ -4604,7 +4604,7 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="n"/>
       <c r="M65" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr"/>
@@ -4669,7 +4669,7 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="n"/>
       <c r="M66" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr"/>
@@ -4734,7 +4734,7 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="n"/>
       <c r="M67" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr"/>
@@ -4864,7 +4864,7 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="n"/>
       <c r="M69" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr"/>
@@ -4929,7 +4929,7 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="n"/>
       <c r="M70" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr"/>
@@ -4994,7 +4994,7 @@
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="n"/>
       <c r="M71" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr"/>
@@ -5059,7 +5059,7 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="n"/>
       <c r="M72" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr"/>
@@ -5124,7 +5124,7 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="n"/>
       <c r="M73" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr"/>
@@ -5189,7 +5189,7 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="n"/>
       <c r="M74" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr"/>
@@ -5254,7 +5254,7 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="n"/>
       <c r="M75" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr"/>
@@ -5319,7 +5319,7 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="n"/>
       <c r="M76" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr"/>
@@ -5384,7 +5384,7 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="n"/>
       <c r="M77" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr"/>
@@ -5449,7 +5449,7 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="n"/>
       <c r="M78" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr"/>
@@ -5514,7 +5514,7 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="n"/>
       <c r="M79" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr"/>
@@ -5579,7 +5579,7 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="n"/>
       <c r="M80" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr"/>
@@ -5644,7 +5644,7 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="n"/>
       <c r="M81" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr"/>
@@ -5709,7 +5709,7 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="n"/>
       <c r="M82" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr"/>
@@ -5774,7 +5774,7 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="n"/>
       <c r="M83" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr"/>
@@ -5839,7 +5839,7 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="n"/>
       <c r="M84" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr"/>
@@ -5904,7 +5904,7 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="n"/>
       <c r="M85" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr"/>
@@ -5969,7 +5969,7 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="n"/>
       <c r="M86" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr"/>
@@ -6034,7 +6034,7 @@
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="n"/>
       <c r="M87" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr"/>
@@ -6099,7 +6099,7 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="n"/>
       <c r="M88" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N88" s="2" t="inlineStr"/>
       <c r="O88" s="2" t="inlineStr"/>
@@ -6164,7 +6164,7 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="n"/>
       <c r="M89" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N89" s="2" t="inlineStr"/>
       <c r="O89" s="2" t="inlineStr"/>
@@ -6294,7 +6294,7 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="n"/>
       <c r="M91" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N91" s="2" t="inlineStr"/>
       <c r="O91" s="2" t="inlineStr"/>
@@ -6359,7 +6359,7 @@
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="n"/>
       <c r="M92" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N92" s="2" t="inlineStr"/>
       <c r="O92" s="2" t="inlineStr"/>
@@ -6424,7 +6424,7 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="n"/>
       <c r="M93" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N93" s="2" t="inlineStr"/>
       <c r="O93" s="2" t="inlineStr"/>
@@ -6489,7 +6489,7 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="n"/>
       <c r="M94" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N94" s="2" t="inlineStr"/>
       <c r="O94" s="2" t="inlineStr"/>
@@ -6554,7 +6554,7 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="n"/>
       <c r="M95" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N95" s="2" t="inlineStr"/>
       <c r="O95" s="2" t="inlineStr"/>
@@ -6619,7 +6619,7 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="n"/>
       <c r="M96" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N96" s="2" t="inlineStr"/>
       <c r="O96" s="2" t="inlineStr"/>
@@ -6684,7 +6684,7 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="n"/>
       <c r="M97" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N97" s="2" t="inlineStr"/>
       <c r="O97" s="2" t="inlineStr"/>
@@ -6749,7 +6749,7 @@
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="n"/>
       <c r="M98" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N98" s="2" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr"/>
@@ -6814,7 +6814,7 @@
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="n"/>
       <c r="M99" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N99" s="2" t="inlineStr"/>
       <c r="O99" s="2" t="inlineStr"/>
@@ -6879,7 +6879,7 @@
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="n"/>
       <c r="M100" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N100" s="2" t="inlineStr"/>
       <c r="O100" s="2" t="inlineStr"/>
@@ -6944,7 +6944,7 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="n"/>
       <c r="M101" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N101" s="2" t="inlineStr"/>
       <c r="O101" s="2" t="inlineStr"/>
@@ -7009,7 +7009,7 @@
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="n"/>
       <c r="M102" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N102" s="2" t="inlineStr"/>
       <c r="O102" s="2" t="inlineStr"/>
@@ -7074,7 +7074,7 @@
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="n"/>
       <c r="M103" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N103" s="2" t="inlineStr"/>
       <c r="O103" s="2" t="inlineStr"/>
@@ -7139,7 +7139,7 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="n"/>
       <c r="M104" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N104" s="2" t="inlineStr"/>
       <c r="O104" s="2" t="inlineStr"/>
@@ -7204,7 +7204,7 @@
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="n"/>
       <c r="M105" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N105" s="2" t="inlineStr"/>
       <c r="O105" s="2" t="inlineStr"/>
@@ -7269,7 +7269,7 @@
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="n"/>
       <c r="M106" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N106" s="2" t="inlineStr"/>
       <c r="O106" s="2" t="inlineStr"/>
@@ -7334,7 +7334,7 @@
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="n"/>
       <c r="M107" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N107" s="2" t="inlineStr"/>
       <c r="O107" s="2" t="inlineStr"/>
@@ -7399,7 +7399,7 @@
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="n"/>
       <c r="M108" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N108" s="2" t="inlineStr"/>
       <c r="O108" s="2" t="inlineStr"/>
@@ -7464,7 +7464,7 @@
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="n"/>
       <c r="M109" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N109" s="2" t="inlineStr"/>
       <c r="O109" s="2" t="inlineStr"/>
@@ -7529,7 +7529,7 @@
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="n"/>
       <c r="M110" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N110" s="2" t="inlineStr"/>
       <c r="O110" s="2" t="inlineStr"/>
@@ -7594,7 +7594,7 @@
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="n"/>
       <c r="M111" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N111" s="2" t="inlineStr"/>
       <c r="O111" s="2" t="inlineStr"/>
@@ -7659,7 +7659,7 @@
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="n"/>
       <c r="M112" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N112" s="2" t="inlineStr"/>
       <c r="O112" s="2" t="inlineStr"/>
@@ -7724,7 +7724,7 @@
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="n"/>
       <c r="M113" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N113" s="2" t="inlineStr"/>
       <c r="O113" s="2" t="inlineStr"/>
@@ -7789,7 +7789,7 @@
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="n"/>
       <c r="M114" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N114" s="2" t="inlineStr"/>
       <c r="O114" s="2" t="inlineStr"/>
@@ -7984,7 +7984,7 @@
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="2" t="n"/>
       <c r="M117" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N117" s="2" t="inlineStr"/>
       <c r="O117" s="2" t="inlineStr"/>
@@ -8049,7 +8049,7 @@
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="n"/>
       <c r="M118" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N118" s="2" t="inlineStr"/>
       <c r="O118" s="2" t="inlineStr"/>
@@ -8114,7 +8114,7 @@
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="2" t="n"/>
       <c r="M119" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N119" s="2" t="inlineStr"/>
       <c r="O119" s="2" t="inlineStr"/>
@@ -8179,7 +8179,7 @@
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="n"/>
       <c r="M120" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N120" s="2" t="inlineStr"/>
       <c r="O120" s="2" t="inlineStr"/>
@@ -8244,7 +8244,7 @@
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="n"/>
       <c r="M121" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N121" s="2" t="inlineStr"/>
       <c r="O121" s="2" t="inlineStr"/>
@@ -8309,7 +8309,7 @@
       <c r="K122" s="2" t="inlineStr"/>
       <c r="L122" s="2" t="n"/>
       <c r="M122" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N122" s="2" t="inlineStr"/>
       <c r="O122" s="2" t="inlineStr"/>
@@ -8374,7 +8374,7 @@
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="n"/>
       <c r="M123" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N123" s="2" t="inlineStr"/>
       <c r="O123" s="2" t="inlineStr"/>
@@ -8439,7 +8439,7 @@
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="n"/>
       <c r="M124" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N124" s="2" t="inlineStr"/>
       <c r="O124" s="2" t="inlineStr"/>
@@ -8699,7 +8699,7 @@
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="n"/>
       <c r="M128" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N128" s="2" t="inlineStr"/>
       <c r="O128" s="2" t="inlineStr"/>
@@ -8764,7 +8764,7 @@
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="2" t="n"/>
       <c r="M129" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N129" s="2" t="inlineStr"/>
       <c r="O129" s="2" t="inlineStr"/>
@@ -8829,7 +8829,7 @@
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="n"/>
       <c r="M130" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N130" s="2" t="inlineStr"/>
       <c r="O130" s="2" t="inlineStr"/>
@@ -8894,7 +8894,7 @@
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="n"/>
       <c r="M131" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N131" s="2" t="inlineStr"/>
       <c r="O131" s="2" t="inlineStr"/>
@@ -9024,7 +9024,7 @@
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="n"/>
       <c r="M133" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N133" s="2" t="inlineStr"/>
       <c r="O133" s="2" t="inlineStr"/>
@@ -9089,7 +9089,7 @@
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="n"/>
       <c r="M134" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N134" s="2" t="inlineStr"/>
       <c r="O134" s="4" t="inlineStr">
@@ -9158,7 +9158,7 @@
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="n"/>
       <c r="M135" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N135" s="2" t="inlineStr"/>
       <c r="O135" s="2" t="inlineStr"/>
@@ -9223,7 +9223,7 @@
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="n"/>
       <c r="M136" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N136" s="2" t="inlineStr"/>
       <c r="O136" s="2" t="inlineStr"/>
@@ -9288,7 +9288,7 @@
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="n"/>
       <c r="M137" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N137" s="2" t="inlineStr"/>
       <c r="O137" s="2" t="inlineStr"/>
@@ -9353,7 +9353,7 @@
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="2" t="n"/>
       <c r="M138" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N138" s="2" t="inlineStr"/>
       <c r="O138" s="2" t="inlineStr"/>
@@ -9418,7 +9418,7 @@
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="n"/>
       <c r="M139" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N139" s="2" t="inlineStr"/>
       <c r="O139" s="2" t="inlineStr"/>
@@ -9483,7 +9483,7 @@
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="n"/>
       <c r="M140" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N140" s="2" t="inlineStr"/>
       <c r="O140" s="2" t="inlineStr"/>
@@ -9548,7 +9548,7 @@
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="n"/>
       <c r="M141" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N141" s="2" t="inlineStr"/>
       <c r="O141" s="2" t="inlineStr"/>
@@ -9613,7 +9613,7 @@
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="n"/>
       <c r="M142" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N142" s="2" t="inlineStr"/>
       <c r="O142" s="2" t="inlineStr"/>
@@ -9808,7 +9808,7 @@
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="n"/>
       <c r="M145" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N145" s="2" t="inlineStr"/>
       <c r="O145" s="2" t="inlineStr"/>
@@ -9873,7 +9873,7 @@
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="n"/>
       <c r="M146" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N146" s="2" t="inlineStr"/>
       <c r="O146" s="2" t="inlineStr"/>
@@ -10003,7 +10003,7 @@
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="n"/>
       <c r="M148" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N148" s="2" t="inlineStr"/>
       <c r="O148" s="2" t="inlineStr"/>
@@ -10068,7 +10068,7 @@
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="n"/>
       <c r="M149" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N149" s="2" t="inlineStr"/>
       <c r="O149" s="2" t="inlineStr"/>
@@ -10133,7 +10133,7 @@
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="n"/>
       <c r="M150" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N150" s="2" t="inlineStr"/>
       <c r="O150" s="2" t="inlineStr"/>
@@ -10263,7 +10263,7 @@
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="n"/>
       <c r="M152" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N152" s="2" t="inlineStr"/>
       <c r="O152" s="2" t="inlineStr"/>
@@ -10328,7 +10328,7 @@
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="n"/>
       <c r="M153" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N153" s="2" t="inlineStr"/>
       <c r="O153" s="2" t="inlineStr"/>
@@ -10424,12 +10424,12 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Баварский Темный береста</t>
+          <t>Баварский Классик береста</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>баварская кладка</t>
+          <t>микс (бавария)</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
@@ -10451,16 +10451,24 @@
         <v>28.4</v>
       </c>
       <c r="J155" s="3" t="n"/>
-      <c r="K155" s="2" t="inlineStr"/>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>0,7НФ (евро): 23.50 ₽</t>
+        </is>
+      </c>
       <c r="L155" s="2" t="n"/>
       <c r="M155" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N155" s="2" t="inlineStr"/>
-      <c r="O155" s="2" t="inlineStr"/>
+      <c r="O155" s="4" t="inlineStr">
+        <is>
+          <t>объединён вариант: БАВАРСКИЙ КЛАССИК Лицевой евро пустотелый М250 (F75) 572шт упак. пленкой</t>
+        </is>
+      </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>Баварский темный Одинарный пустотелый М175 (F75) 416шт упак. пленкой</t>
+          <t>БАВАРСКИЙ КЛАССИК Лицевой Одинарный М175 (F75) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -10487,43 +10495,51 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>Баварский Светлый береста</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>микс (бавария)</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>бежевый</t>
+          <t>микс (бавария)</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>ручная формовка</t>
+          <t>береста</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>WDF</t>
+          <t>1НФ (одинарный)</t>
         </is>
       </c>
       <c r="I156" s="3" t="n">
-        <v>68.2</v>
+        <v>28.4</v>
       </c>
       <c r="J156" s="3" t="n"/>
-      <c r="K156" s="2" t="inlineStr"/>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>0,7НФ (евро): 23.50 ₽</t>
+        </is>
+      </c>
       <c r="L156" s="2" t="n"/>
       <c r="M156" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N156" s="2" t="inlineStr"/>
-      <c r="O156" s="2" t="inlineStr"/>
+      <c r="O156" s="4" t="inlineStr">
+        <is>
+          <t>объединён вариант: БАВАРСКИЙ СВЕТЛЫЙ Лицевой евро пустотелый М250 (F75) 572шт упак. пленкой</t>
+        </is>
+      </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>"Бронза" Кирпич полнотелй ручной формовки М150 (F50 WDF ТУ) 556шт</t>
+          <t>БАВАРСКИЙ СВЕТЛЫЙ Лицевой Одинарный М175 (F75) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -10550,17 +10566,17 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Вельвет</t>
+          <t>Баварский Темный береста</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>баварская кладка</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>микс (бавария)</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -10574,19 +10590,19 @@
         </is>
       </c>
       <c r="I157" s="3" t="n">
-        <v>23.8</v>
+        <v>28.4</v>
       </c>
       <c r="J157" s="3" t="n"/>
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="2" t="n"/>
       <c r="M157" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N157" s="2" t="inlineStr"/>
       <c r="O157" s="2" t="inlineStr"/>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>Вельвет Лицевой Одинарный Гладкий М175 (F75) 480шт упак. пленкой</t>
+          <t>Баварский темный Одинарный пустотелый М175 (F75) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -10613,47 +10629,43 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Винтаж</t>
+          <t>Бронза</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>баварская кладка</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>микс (бавария)</t>
+          <t>бежевый</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>береста</t>
+          <t>ручная формовка</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>1НФ (одинарный)</t>
+          <t>WDF</t>
         </is>
       </c>
       <c r="I158" s="3" t="n">
-        <v>29.2</v>
+        <v>68.2</v>
       </c>
       <c r="J158" s="3" t="n"/>
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="n"/>
-      <c r="M158" s="5" t="n">
-        <v>0</v>
+      <c r="M158" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="N158" s="2" t="inlineStr"/>
-      <c r="O158" s="4" t="inlineStr">
-        <is>
-          <t>нет фото</t>
-        </is>
-      </c>
+      <c r="O158" s="2" t="inlineStr"/>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>ВИНТАЖ Одинарный пустотелый М175 (F75 пустот 37%) 416шт упак. пленкой</t>
+          <t>"Бронза" Кирпич полнотелй ручной формовки М150 (F50 WDF ТУ) 556шт</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -10680,7 +10692,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Винтаж Лава</t>
+          <t>Булат</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -10695,7 +10707,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>береста</t>
+          <t>фактурный</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -10704,19 +10716,19 @@
         </is>
       </c>
       <c r="I159" s="3" t="n">
-        <v>29.2</v>
+        <v>32.4</v>
       </c>
       <c r="J159" s="3" t="n"/>
       <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="n"/>
       <c r="M159" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N159" s="2" t="inlineStr"/>
       <c r="O159" s="2" t="inlineStr"/>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>Винтаж лава Одинарный пустотелый М175 (F75 пустот 37%) 416шт упак. пленкой</t>
+          <t>БУЛАТ Лицевой Одинарный М175 (F75) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -10743,12 +10755,12 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Вишня</t>
+          <t>Вельвет</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>вишня</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
@@ -10758,7 +10770,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>гладкий</t>
+          <t>береста</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -10767,23 +10779,19 @@
         </is>
       </c>
       <c r="I160" s="3" t="n">
-        <v>36.7</v>
+        <v>23.8</v>
       </c>
       <c r="J160" s="3" t="n"/>
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="n"/>
       <c r="M160" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N160" s="2" t="inlineStr"/>
-      <c r="O160" s="4" t="inlineStr">
-        <is>
-          <t>вариант фасовки: ВИШНЯ Лицевой Одинарный М150 (F50) 480шт упак. пленкой</t>
-        </is>
-      </c>
+      <c r="O160" s="2" t="inlineStr"/>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>ВИШНЯ Лицевой Одинарный М150 (F50) 416шт упак. пленкой</t>
+          <t>Вельвет Лицевой Одинарный Гладкий М175 (F75) 480шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -10810,17 +10818,17 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Вишня Береста</t>
+          <t>Винтаж</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>вишня</t>
+          <t>баварская кладка</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>микс (бавария)</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -10834,7 +10842,7 @@
         </is>
       </c>
       <c r="I161" s="3" t="n">
-        <v>36.7</v>
+        <v>29.2</v>
       </c>
       <c r="J161" s="3" t="n"/>
       <c r="K161" s="2" t="inlineStr"/>
@@ -10850,7 +10858,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>ВИШНЯ Береста Лицевой Одинарный М150 (F50) 416шт упак. пленкой</t>
+          <t>ВИНТАЖ Одинарный пустотелый М175 (F75 пустот 37%) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -10877,17 +10885,17 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Вишня Руст</t>
+          <t>Винтаж Лава</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>вишня</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
@@ -10901,23 +10909,19 @@
         </is>
       </c>
       <c r="I162" s="3" t="n">
-        <v>36.7</v>
+        <v>29.2</v>
       </c>
       <c r="J162" s="3" t="n"/>
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="n"/>
-      <c r="M162" s="5" t="n">
-        <v>0</v>
+      <c r="M162" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="N162" s="2" t="inlineStr"/>
-      <c r="O162" s="4" t="inlineStr">
-        <is>
-          <t>нет фото</t>
-        </is>
-      </c>
+      <c r="O162" s="2" t="inlineStr"/>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>ВИШНЯ Руст Лицевой Одинарный М150 (F50) 416шт упак. пленкой</t>
+          <t>Винтаж лава Одинарный пустотелый М175 (F75 пустот 37%) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -10944,17 +10948,17 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Вулкан Лава</t>
+          <t>Винтаж Лайт</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -10968,19 +10972,19 @@
         </is>
       </c>
       <c r="I163" s="3" t="n">
-        <v>28.6</v>
+        <v>29.2</v>
       </c>
       <c r="J163" s="3" t="n"/>
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="n"/>
       <c r="M163" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N163" s="2" t="inlineStr"/>
       <c r="O163" s="2" t="inlineStr"/>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>Вулкан лава Одинарный пустотелый М175 (F75 пустот 37%) 416шт упак. пленкой</t>
+          <t>ВИНТАЖ ЛАЙТ Лицевой Одинарный М175 (F75) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q163" s="2" t="inlineStr">
@@ -11007,17 +11011,17 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Вулкан береста</t>
+          <t>Винтаж Премиум</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -11031,19 +11035,19 @@
         </is>
       </c>
       <c r="I164" s="3" t="n">
-        <v>28.6</v>
+        <v>29.2</v>
       </c>
       <c r="J164" s="3" t="n"/>
       <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="2" t="n"/>
       <c r="M164" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N164" s="2" t="inlineStr"/>
       <c r="O164" s="2" t="inlineStr"/>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>Вулкан Одинарный пустотелый М175 (F75 пустот 37%) 416шт упак. пленкой</t>
+          <t>ВИНТАЖ ПРЕМИУМ Лицевой Одинарный М175 (F75) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q164" s="2" t="inlineStr">
@@ -11070,22 +11074,22 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Готик руст</t>
+          <t>Вишня</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>коричневый</t>
+          <t>вишня</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>коричневый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>руст</t>
+          <t>гладкий</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -11094,27 +11098,23 @@
         </is>
       </c>
       <c r="I165" s="3" t="n">
-        <v>29.2</v>
+        <v>36.7</v>
       </c>
       <c r="J165" s="3" t="n"/>
-      <c r="K165" s="2" t="inlineStr">
-        <is>
-          <t>1,4НФ (полуторный): 39.75 ₽</t>
-        </is>
-      </c>
+      <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="2" t="n"/>
       <c r="M165" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N165" s="2" t="inlineStr"/>
       <c r="O165" s="4" t="inlineStr">
         <is>
-          <t>объединён вариант: Готик Утолщенный пустотелый М175 (F75) 320шт упак. пленкой</t>
+          <t>вариант фасовки: ВИШНЯ Лицевой Одинарный М150 (F50) 480шт упак. пленкой</t>
         </is>
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>Готик Одинарный пустотелый М175 (F75 пустот 37%) 416шт упак. пленкой</t>
+          <t>ВИШНЯ Лицевой Одинарный М150 (F50) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q165" s="2" t="inlineStr">
@@ -11141,17 +11141,17 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Гранит береста</t>
+          <t>Вишня Береста</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>коричневый</t>
+          <t>вишня</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>серый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
@@ -11165,19 +11165,23 @@
         </is>
       </c>
       <c r="I166" s="3" t="n">
-        <v>33.5</v>
+        <v>36.7</v>
       </c>
       <c r="J166" s="3" t="n"/>
       <c r="K166" s="2" t="inlineStr"/>
       <c r="L166" s="2" t="n"/>
-      <c r="M166" s="2" t="n">
-        <v>6</v>
+      <c r="M166" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="N166" s="2" t="inlineStr"/>
-      <c r="O166" s="2" t="inlineStr"/>
+      <c r="O166" s="4" t="inlineStr">
+        <is>
+          <t>нет фото</t>
+        </is>
+      </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>Гранит Одинарный пустотелый М175 (F75 пустот 37%) 416шт упак. пленкой</t>
+          <t>ВИШНЯ Береста Лицевой Одинарный М150 (F50) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
@@ -11204,22 +11208,22 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Коричневый</t>
+          <t>Вишня Руст</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>коричневый</t>
+          <t>вишня</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>коричневый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>гладкий</t>
+          <t>береста</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -11228,27 +11232,23 @@
         </is>
       </c>
       <c r="I167" s="3" t="n">
-        <v>37.7</v>
+        <v>36.7</v>
       </c>
       <c r="J167" s="3" t="n"/>
-      <c r="K167" s="2" t="inlineStr">
-        <is>
-          <t>1,4НФ (полуторный): 47.40 ₽</t>
-        </is>
-      </c>
+      <c r="K167" s="2" t="inlineStr"/>
       <c r="L167" s="2" t="n"/>
-      <c r="M167" s="2" t="n">
-        <v>1</v>
+      <c r="M167" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="N167" s="2" t="inlineStr"/>
       <c r="O167" s="4" t="inlineStr">
         <is>
-          <t>объединён вариант: КОРИЧНЕВЫЙ Лицевой УТОЛЩЕННЫЙ М150 (F50) 320шт упак. пленкой</t>
+          <t>нет фото</t>
         </is>
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>КОРИЧНЕВЫЙ Лицевой Одинарный М150 (F50) 480шт упак. пленкой</t>
+          <t>ВИШНЯ Руст Лицевой Одинарный М150 (F50) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -11275,17 +11275,17 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Коричневый береста</t>
+          <t>Вулкан Лава</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>коричневый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>коричневый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
@@ -11299,27 +11299,19 @@
         </is>
       </c>
       <c r="I168" s="3" t="n">
-        <v>37.7</v>
+        <v>28.6</v>
       </c>
       <c r="J168" s="3" t="n"/>
-      <c r="K168" s="2" t="inlineStr">
-        <is>
-          <t>1,4НФ (полуторный): 47.40 ₽</t>
-        </is>
-      </c>
+      <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="2" t="n"/>
       <c r="M168" s="2" t="n">
         <v>6</v>
       </c>
       <c r="N168" s="2" t="inlineStr"/>
-      <c r="O168" s="4" t="inlineStr">
-        <is>
-          <t>объединён вариант: КОРИЧНЕВЫЙ Лицевой УТОЛЩЕННЫЙ М175 (F75) 320шт упак. пленкой</t>
-        </is>
-      </c>
+      <c r="O168" s="2" t="inlineStr"/>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>КОРИЧНЕВЫЙ Лицевой Одинарный Гладкий М175 (F75) 416шт упак. пленкой</t>
+          <t>Вулкан лава Одинарный пустотелый М175 (F75 пустот 37%) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -11346,22 +11338,22 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Коричневый руст</t>
+          <t>Вулкан береста</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>коричневый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>коричневый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>руст</t>
+          <t>береста</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -11370,19 +11362,19 @@
         </is>
       </c>
       <c r="I169" s="3" t="n">
-        <v>37.7</v>
+        <v>28.6</v>
       </c>
       <c r="J169" s="3" t="n"/>
       <c r="K169" s="2" t="inlineStr"/>
       <c r="L169" s="2" t="n"/>
       <c r="M169" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N169" s="2" t="inlineStr"/>
       <c r="O169" s="2" t="inlineStr"/>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>КОРИЧНЕВЫЙ Лицевой Одинарный "РУСТ" М150 (F50) 416шт упак. пленкой</t>
+          <t>Вулкан Одинарный пустотелый М175 (F75 пустот 37%) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -11409,22 +11401,22 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Красный</t>
+          <t>Готик руст</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>гладкий</t>
+          <t>руст</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -11433,27 +11425,27 @@
         </is>
       </c>
       <c r="I170" s="3" t="n">
-        <v>22.3</v>
+        <v>29.2</v>
       </c>
       <c r="J170" s="3" t="n"/>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>1,4НФ (полуторный): 33.30 ₽</t>
+          <t>1,4НФ (полуторный): 39.75 ₽</t>
         </is>
       </c>
       <c r="L170" s="2" t="n"/>
       <c r="M170" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N170" s="2" t="inlineStr"/>
       <c r="O170" s="4" t="inlineStr">
         <is>
-          <t>объединён вариант: КРАСНЫЙ Лицевой УТОЛЩЕННЫЙ М150 (F50) 320шт упак. пленкой</t>
+          <t>объединён вариант: Готик Утолщенный пустотелый М175 (F75) 320шт упак. пленкой</t>
         </is>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>КРАСНЫЙ Одинарный М175 (F75) 416шт упак. пленкой,</t>
+          <t>Готик Одинарный пустотелый М175 (F75 пустот 37%) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -11480,17 +11472,17 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Красный Береста</t>
+          <t>Гранит береста</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
@@ -11504,27 +11496,19 @@
         </is>
       </c>
       <c r="I171" s="3" t="n">
-        <v>22.8</v>
+        <v>33.5</v>
       </c>
       <c r="J171" s="3" t="n"/>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>1,4НФ (полуторный): 33.30 ₽</t>
-        </is>
-      </c>
+      <c r="K171" s="2" t="inlineStr"/>
       <c r="L171" s="2" t="n"/>
       <c r="M171" s="2" t="n">
         <v>6</v>
       </c>
       <c r="N171" s="2" t="inlineStr"/>
-      <c r="O171" s="4" t="inlineStr">
-        <is>
-          <t>вариант фасовки: КРАСНЫЙ "БЕРЕСТА" Лицевой Одинарный М150 (F50 пустот 37%) 480шт упак. пленкой; объединён вариант: КРАСНЫЙ Лицевой УТОЛЩЕННЫЙ "Береста" М175 (F50) 320шт упак. пленкой</t>
-        </is>
-      </c>
+      <c r="O171" s="2" t="inlineStr"/>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>КРАСНЫЙ "БЕРЕСТА" Лицевой Одинарный М150 (F50 пустот 37%) 416шт упак. пленкой</t>
+          <t>Гранит Одинарный пустотелый М175 (F75 пустот 37%) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -11551,22 +11535,22 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Красный Рельефный</t>
+          <t>Коричневый</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>береста</t>
+          <t>гладкий</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -11575,23 +11559,27 @@
         </is>
       </c>
       <c r="I172" s="3" t="n">
-        <v>22.8</v>
+        <v>37.7</v>
       </c>
       <c r="J172" s="3" t="n"/>
-      <c r="K172" s="2" t="inlineStr"/>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>1,4НФ (полуторный): 47.40 ₽</t>
+        </is>
+      </c>
       <c r="L172" s="2" t="n"/>
-      <c r="M172" s="5" t="n">
-        <v>0</v>
+      <c r="M172" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="N172" s="2" t="inlineStr"/>
       <c r="O172" s="4" t="inlineStr">
         <is>
-          <t>нет фото; объединена фасовка: КРАСНЫЙ РЕЛЬЕФНЫЙ Одинарный М150 (F50) 480шт упак. пленкой</t>
+          <t>объединён вариант: КОРИЧНЕВЫЙ Лицевой УТОЛЩЕННЫЙ М150 (F50) 320шт упак. пленкой</t>
         </is>
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>КРАСНЫЙ Рельефный Лицевой Одинарный М150 (F50 пустот 37%) 416шт упак. пленкой</t>
+          <t>КОРИЧНЕВЫЙ Лицевой Одинарный М150 (F50) 480шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -11618,22 +11606,22 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Красный Руст</t>
+          <t>Коричневый Сахара</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>руст</t>
+          <t>сахара</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -11642,27 +11630,19 @@
         </is>
       </c>
       <c r="I173" s="3" t="n">
-        <v>22.8</v>
+        <v>37.7</v>
       </c>
       <c r="J173" s="3" t="n"/>
-      <c r="K173" s="2" t="inlineStr">
-        <is>
-          <t>1,4НФ (полуторный): 33.30 ₽</t>
-        </is>
-      </c>
+      <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="n"/>
       <c r="M173" s="2" t="n">
         <v>6</v>
       </c>
       <c r="N173" s="2" t="inlineStr"/>
-      <c r="O173" s="4" t="inlineStr">
-        <is>
-          <t>вариант фасовки: КРАСНЫЙ "РУСТ" Лицевой Одинарный М150 (F50 пустот 37%) 480шт упак. пленкой; объединён вариант: КРАСНЫЙ Лицевой УТОЛЩЕННЫЙ "Руст" М175 (F50) 320шт упак. пленкой</t>
-        </is>
-      </c>
+      <c r="O173" s="2" t="inlineStr"/>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>КРАСНЫЙ "РУСТ" Лицевой Одинарный М150 (F50 пустот 37%) 416шт упак. пленкой</t>
+          <t>КОРИЧНЕВЫЙ САХАРА Лицевой Одинарный М150 (F50) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -11689,43 +11669,51 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Латунь</t>
+          <t>Коричневый Скала Антик</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>бежевый</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>ручная формовка</t>
+          <t>антик</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>WDF</t>
+          <t>1НФ (одинарный)</t>
         </is>
       </c>
       <c r="I174" s="3" t="n">
-        <v>68.2</v>
+        <v>37.7</v>
       </c>
       <c r="J174" s="3" t="n"/>
-      <c r="K174" s="2" t="inlineStr"/>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>1,4НФ (полуторный): 47.40 ₽</t>
+        </is>
+      </c>
       <c r="L174" s="2" t="n"/>
       <c r="M174" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N174" s="2" t="inlineStr"/>
-      <c r="O174" s="2" t="inlineStr"/>
+      <c r="O174" s="4" t="inlineStr">
+        <is>
+          <t>объединён вариант: КОРИЧНЕВЫЙ СКАЛА АНТИК Лицевой УТОЛЩЕННЫЙ М175 (F75) 320шт упак. пленкой</t>
+        </is>
+      </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>"Латунь" Кирпич полнотелй ручной формовки М150 (F50 WDF ТУ) 556шт</t>
+          <t>КОРИЧНЕВЫЙ СКАЛА АНТИК Лицевой Одинарный М175 (F75) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -11752,43 +11740,51 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Медь</t>
+          <t>Коричневый береста</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>ручная формовка</t>
+          <t>береста</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>WDF</t>
+          <t>1НФ (одинарный)</t>
         </is>
       </c>
       <c r="I175" s="3" t="n">
-        <v>66</v>
+        <v>37.7</v>
       </c>
       <c r="J175" s="3" t="n"/>
-      <c r="K175" s="2" t="inlineStr"/>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>1,4НФ (полуторный): 47.40 ₽</t>
+        </is>
+      </c>
       <c r="L175" s="2" t="n"/>
       <c r="M175" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N175" s="2" t="inlineStr"/>
-      <c r="O175" s="2" t="inlineStr"/>
+      <c r="O175" s="4" t="inlineStr">
+        <is>
+          <t>объединён вариант: КОРИЧНЕВЫЙ Лицевой УТОЛЩЕННЫЙ М175 (F75) 320шт упак. пленкой</t>
+        </is>
+      </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>"Медь" Кирпич полнотелый ручной формовки М150 (F50 WDF ТУ) 556штF50</t>
+          <t>КОРИЧНЕВЫЙ Лицевой Одинарный Гладкий М175 (F75) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -11815,43 +11811,43 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Патина</t>
+          <t>Коричневый руст</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>ручная формовка</t>
+          <t>руст</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>WDF</t>
+          <t>1НФ (одинарный)</t>
         </is>
       </c>
       <c r="I176" s="3" t="n">
-        <v>68.2</v>
+        <v>37.7</v>
       </c>
       <c r="J176" s="3" t="n"/>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="n"/>
       <c r="M176" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N176" s="2" t="inlineStr"/>
       <c r="O176" s="2" t="inlineStr"/>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>"Патина" Кирпич полнотелый ручной формовки М150 (F50 WDF ТУ) 556штF50</t>
+          <t>КОРИЧНЕВЫЙ Лицевой Одинарный "РУСТ" М150 (F50) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -11878,22 +11874,22 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Персик коралл</t>
+          <t>Красный</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>персик</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>персиковый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>коралл</t>
+          <t>гладкий</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -11901,18 +11897,28 @@
           <t>1НФ (одинарный)</t>
         </is>
       </c>
-      <c r="I177" s="3" t="n"/>
+      <c r="I177" s="3" t="n">
+        <v>22.3</v>
+      </c>
       <c r="J177" s="3" t="n"/>
-      <c r="K177" s="2" t="inlineStr"/>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>1,4НФ (полуторный): 33.30 ₽</t>
+        </is>
+      </c>
       <c r="L177" s="2" t="n"/>
       <c r="M177" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N177" s="2" t="inlineStr"/>
-      <c r="O177" s="2" t="inlineStr"/>
+      <c r="O177" s="4" t="inlineStr">
+        <is>
+          <t>объединён вариант: КРАСНЫЙ Лицевой УТОЛЩЕННЫЙ М150 (F50) 320шт упак. пленкой</t>
+        </is>
+      </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>"ПЕРСИК" Рядовой Одинарный Гладкий М150 (F50) 416шт упак. пленкой</t>
+          <t>КРАСНЫЙ Одинарный М175 (F75) 416шт упак. пленкой,</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -11939,22 +11945,22 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Светлосерый</t>
+          <t>Красный Береста</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>светлый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>серый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>гладкий</t>
+          <t>береста</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -11963,19 +11969,27 @@
         </is>
       </c>
       <c r="I178" s="3" t="n">
-        <v>32.4</v>
+        <v>22.8</v>
       </c>
       <c r="J178" s="3" t="n"/>
-      <c r="K178" s="2" t="inlineStr"/>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>1,4НФ (полуторный): 33.30 ₽</t>
+        </is>
+      </c>
       <c r="L178" s="2" t="n"/>
       <c r="M178" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N178" s="2" t="inlineStr"/>
-      <c r="O178" s="2" t="inlineStr"/>
+      <c r="O178" s="4" t="inlineStr">
+        <is>
+          <t>вариант фасовки: КРАСНЫЙ "БЕРЕСТА" Лицевой Одинарный М150 (F50 пустот 37%) 480шт упак. пленкой; объединён вариант: КРАСНЫЙ Лицевой УТОЛЩЕННЫЙ "Береста" М175 (F50) 320шт упак. пленкой</t>
+        </is>
+      </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>Светлосерый кирпич "МРАМОР" M150 (F50) 416шт упак. пленкой</t>
+          <t>КРАСНЫЙ "БЕРЕСТА" Лицевой Одинарный М150 (F50 пустот 37%) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -12002,22 +12016,22 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Светлый</t>
+          <t>Красный Рельефный</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>светлый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>бежевый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>гладкий</t>
+          <t>береста</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -12026,27 +12040,23 @@
         </is>
       </c>
       <c r="I179" s="3" t="n">
-        <v>28</v>
+        <v>22.8</v>
       </c>
       <c r="J179" s="3" t="n"/>
-      <c r="K179" s="2" t="inlineStr">
-        <is>
-          <t>1НФ (одинарный), марка М150: 43.20 ₽; 1,4НФ (полуторный): 46.55 ₽</t>
-        </is>
-      </c>
+      <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="n"/>
-      <c r="M179" s="2" t="n">
-        <v>2</v>
+      <c r="M179" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="N179" s="2" t="inlineStr"/>
       <c r="O179" s="4" t="inlineStr">
         <is>
-          <t>объединён вариант: Светлый кирпич "СЛОНОВАЯ КОСТЬ" Одинарный пустотелый М150 (F50 пустот 37%) 416шт; объединён вариант: СВЕТЛЫЙ УТОЛЩЕННЫЙ ЛИЦЕВОЙ с ФАСКОЙ M175 (F75) 320шт упак. в пленку</t>
+          <t>нет фото; объединена фасовка: КРАСНЫЙ РЕЛЬЕФНЫЙ Одинарный М150 (F50) 480шт упак. пленкой</t>
         </is>
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>СВЕТЛЫЙ одинарный ЛИЦЕВОЙ с ФАСКОЙ M150 (F50) 416шт упак. пленкой</t>
+          <t>КРАСНЫЙ Рельефный Лицевой Одинарный М150 (F50 пустот 37%) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -12073,22 +12083,22 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Светлый Винтаж</t>
+          <t>Красный Руст</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>светлый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>бежевый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>береста</t>
+          <t>руст</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -12097,19 +12107,27 @@
         </is>
       </c>
       <c r="I180" s="3" t="n">
-        <v>36.4</v>
+        <v>22.8</v>
       </c>
       <c r="J180" s="3" t="n"/>
-      <c r="K180" s="2" t="inlineStr"/>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>1,4НФ (полуторный): 33.30 ₽</t>
+        </is>
+      </c>
       <c r="L180" s="2" t="n"/>
       <c r="M180" s="2" t="n">
         <v>6</v>
       </c>
       <c r="N180" s="2" t="inlineStr"/>
-      <c r="O180" s="2" t="inlineStr"/>
+      <c r="O180" s="4" t="inlineStr">
+        <is>
+          <t>вариант фасовки: КРАСНЫЙ "РУСТ" Лицевой Одинарный М150 (F50 пустот 37%) 480шт упак. пленкой; объединён вариант: КРАСНЫЙ Лицевой УТОЛЩЕННЫЙ "Руст" М175 (F50) 320шт упак. пленкой</t>
+        </is>
+      </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>СВЕТЛЫЙ ВИНТАЖ Одинарный пустотелый М150 (F50 пустот 37%) 416шт упак. пленкой</t>
+          <t>КРАСНЫЙ "РУСТ" Лицевой Одинарный М150 (F50 пустот 37%) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -12136,22 +12154,22 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Скала рельефный</t>
+          <t>Красный Сахара</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>коричневый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>серый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>рельефный</t>
+          <t>сахара</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
@@ -12160,19 +12178,19 @@
         </is>
       </c>
       <c r="I181" s="3" t="n">
-        <v>22.8</v>
+        <v>22.3</v>
       </c>
       <c r="J181" s="3" t="n"/>
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="n"/>
       <c r="M181" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N181" s="2" t="inlineStr"/>
       <c r="O181" s="2" t="inlineStr"/>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>Скала Лицевой Одинарный Гладкий М150 (F50) 416шт упак. пленкой</t>
+          <t>КРАСНЫЙ САХАРА Лицевой Одинарный М175 (F75) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -12199,22 +12217,22 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Солома</t>
+          <t>Красный Скала Антик</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>солома</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>бежевый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>гладкий</t>
+          <t>антик</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
@@ -12223,27 +12241,19 @@
         </is>
       </c>
       <c r="I182" s="3" t="n">
-        <v>35.15</v>
+        <v>22.3</v>
       </c>
       <c r="J182" s="3" t="n"/>
-      <c r="K182" s="2" t="inlineStr">
-        <is>
-          <t>1НФ (одинарный), марка М175: 35.15 ₽</t>
-        </is>
-      </c>
+      <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="n"/>
       <c r="M182" s="2" t="n">
         <v>6</v>
       </c>
       <c r="N182" s="2" t="inlineStr"/>
-      <c r="O182" s="4" t="inlineStr">
-        <is>
-          <t>объединён вариант: "СОЛОМА" Лицевой Одинарный Гладкий М175 (F50) 416шт упак. пленкой</t>
-        </is>
-      </c>
+      <c r="O182" s="2" t="inlineStr"/>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>"СОЛОМА" Лицевой Одинарный Гладкий М150 (F50) 480шт упак. пленкой</t>
+          <t>КРАСНЫЙ СКАЛА АНТИК Лицевой Одинарный М175 (F75) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -12270,12 +12280,12 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Солома береста</t>
+          <t>Латунь</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>солома</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
@@ -12285,36 +12295,28 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>береста</t>
+          <t>ручная формовка</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>1,4НФ (полуторный)</t>
+          <t>WDF</t>
         </is>
       </c>
       <c r="I183" s="3" t="n">
-        <v>44.25</v>
+        <v>68.2</v>
       </c>
       <c r="J183" s="3" t="n"/>
-      <c r="K183" s="2" t="inlineStr">
-        <is>
-          <t>1НФ (одинарный): 35.15 ₽</t>
-        </is>
-      </c>
+      <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="n"/>
       <c r="M183" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N183" s="2" t="inlineStr"/>
-      <c r="O183" s="4" t="inlineStr">
-        <is>
-          <t>объединён вариант: "СОЛОМА" Лицевой Одинарный "Коралл" М175 (F50) 416шт упак пленкой</t>
-        </is>
-      </c>
+      <c r="O183" s="2" t="inlineStr"/>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>"СОЛОМА" Лицевой Утолщенный М175 (F75) 320шт упак. пленкой</t>
+          <t>"Латунь" Кирпич полнотелй ручной формовки М150 (F50 WDF ТУ) 556шт</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -12341,47 +12343,43 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Солома коралл</t>
+          <t>Медь</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>солома</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>бежевый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>коралл</t>
+          <t>ручная формовка</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>1НФ (одинарный)</t>
+          <t>WDF</t>
         </is>
       </c>
       <c r="I184" s="3" t="n">
-        <v>29.95</v>
+        <v>66</v>
       </c>
       <c r="J184" s="3" t="n"/>
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="2" t="n"/>
-      <c r="M184" s="5" t="n">
-        <v>0</v>
+      <c r="M184" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="N184" s="2" t="inlineStr"/>
-      <c r="O184" s="4" t="inlineStr">
-        <is>
-          <t>нет фото</t>
-        </is>
-      </c>
+      <c r="O184" s="2" t="inlineStr"/>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>"СОЛОМА" Лицевой Одинарный "Коралл" М150 (F50) 480шт упак. пленкой</t>
+          <t>"Медь" Кирпич полнотелый ручной формовки М150 (F50 WDF ТУ) 556штF50</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -12408,7 +12406,7 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Тархан рельефный</t>
+          <t>Патина</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -12423,28 +12421,28 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>рельефный</t>
+          <t>ручная формовка</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>1НФ (одинарный)</t>
+          <t>WDF</t>
         </is>
       </c>
       <c r="I185" s="3" t="n">
-        <v>32.5</v>
+        <v>68.2</v>
       </c>
       <c r="J185" s="3" t="n"/>
       <c r="K185" s="2" t="inlineStr"/>
       <c r="L185" s="2" t="n"/>
       <c r="M185" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N185" s="2" t="inlineStr"/>
       <c r="O185" s="2" t="inlineStr"/>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>"ТАРХАН" Одинарный пустотелый М175 (F75) 416 шт.</t>
+          <t>"Патина" Кирпич полнотелый ручной формовки М150 (F50 WDF ТУ) 556штF50</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -12471,32 +12469,30 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Феррум</t>
+          <t>Персик коралл</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>персик</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>персиковый</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>ручная формовка</t>
+          <t>коралл</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>WDF</t>
-        </is>
-      </c>
-      <c r="I186" s="3" t="n">
-        <v>68.2</v>
-      </c>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I186" s="3" t="n"/>
       <c r="J186" s="3" t="n"/>
       <c r="K186" s="2" t="inlineStr"/>
       <c r="L186" s="2" t="n"/>
@@ -12507,7 +12503,7 @@
       <c r="O186" s="2" t="inlineStr"/>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>"Феррум" Кирпич полнотелй ручной формовки М150 (F50 WDF ТУ) 556шт</t>
+          <t>"ПЕРСИК" Рядовой Одинарный Гладкий М150 (F50) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -12519,12 +12515,12 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>pal-001</t>
+          <t>kla-034</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Палитра</t>
+          <t>Классика</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -12534,17 +12530,17 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Абрикос</t>
+          <t>Светлосерый</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>Розовый</t>
+          <t>светлый</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>персиковый</t>
+          <t>серый</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
@@ -12558,46 +12554,36 @@
         </is>
       </c>
       <c r="I187" s="3" t="n">
-        <v>36.88</v>
+        <v>32.4</v>
       </c>
       <c r="J187" s="3" t="n"/>
-      <c r="K187" s="2" t="inlineStr">
-        <is>
-          <t>0,7НФ (евро): 34.00 ₽; 0,9НФ: 36.88 ₽; 1,4НФ (полуторный): 47.78 ₽</t>
-        </is>
-      </c>
-      <c r="L187" s="2" t="n">
-        <v>51.4</v>
-      </c>
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="2" t="n"/>
       <c r="M187" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N187" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="N187" s="2" t="inlineStr"/>
       <c r="O187" s="2" t="inlineStr"/>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>Абрикос</t>
+          <t>Светлосерый кирпич "МРАМОР" M150 (F50) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
         <is>
-          <t>Губский</t>
+          <t>Донской</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>pal-002</t>
+          <t>kla-035</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Палитра</t>
+          <t>Классика</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -12607,17 +12593,17 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Амбрим</t>
+          <t>Светлый</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>Красный</t>
+          <t>светлый</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>бежевый</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -12631,46 +12617,44 @@
         </is>
       </c>
       <c r="I188" s="3" t="n">
-        <v>26.48</v>
+        <v>28</v>
       </c>
       <c r="J188" s="3" t="n"/>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>1,4НФ (полуторный): 33.62 ₽</t>
-        </is>
-      </c>
-      <c r="L188" s="2" t="n">
-        <v>51.4</v>
-      </c>
+          <t>1НФ (одинарный), марка М150: 43.20 ₽; 1,4НФ (полуторный): 46.55 ₽</t>
+        </is>
+      </c>
+      <c r="L188" s="2" t="n"/>
       <c r="M188" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N188" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="O188" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N188" s="2" t="inlineStr"/>
+      <c r="O188" s="4" t="inlineStr">
+        <is>
+          <t>объединён вариант: Светлый кирпич "СЛОНОВАЯ КОСТЬ" Одинарный пустотелый М150 (F50 пустот 37%) 416шт; объединён вариант: СВЕТЛЫЙ УТОЛЩЕННЫЙ ЛИЦЕВОЙ с ФАСКОЙ M175 (F75) 320шт упак. в пленку</t>
+        </is>
+      </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>Амбрим</t>
+          <t>СВЕТЛЫЙ одинарный ЛИЦЕВОЙ с ФАСКОЙ M150 (F50) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
         <is>
-          <t>Губский</t>
+          <t>Донской</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>pal-003</t>
+          <t>kla-036</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Палитра</t>
+          <t>Классика</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -12680,12 +12664,12 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Бежевая Кора</t>
+          <t>Светлый Береста</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>Бежевый</t>
+          <t>желтый</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
@@ -12695,7 +12679,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>кора</t>
+          <t>береста</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -12704,42 +12688,36 @@
         </is>
       </c>
       <c r="I189" s="3" t="n">
-        <v>45.86</v>
+        <v>28</v>
       </c>
       <c r="J189" s="3" t="n"/>
-      <c r="K189" s="2" t="inlineStr">
-        <is>
-          <t>0,7НФ (евро): 42.50 ₽; 1,4НФ (полуторный): 56.77 ₽</t>
-        </is>
-      </c>
-      <c r="L189" s="2" t="n">
-        <v>51.4</v>
-      </c>
+      <c r="K189" s="2" t="inlineStr"/>
+      <c r="L189" s="2" t="n"/>
       <c r="M189" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N189" s="2" t="inlineStr"/>
       <c r="O189" s="2" t="inlineStr"/>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>Бежевая кора</t>
+          <t>СВЕТЛЫЙ БЕРЕСТА Лицевой Одинарный М150 (F50) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
         <is>
-          <t>Губский</t>
+          <t>Донской</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>pal-004</t>
+          <t>kla-037</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Палитра</t>
+          <t>Классика</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -12749,12 +12727,12 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Бежевый Бриз</t>
+          <t>Светлый Винтаж</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>Бежевый</t>
+          <t>светлый</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
@@ -12764,7 +12742,7 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>бриз</t>
+          <t>береста</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
@@ -12773,42 +12751,36 @@
         </is>
       </c>
       <c r="I190" s="3" t="n">
-        <v>45.86</v>
+        <v>36.4</v>
       </c>
       <c r="J190" s="3" t="n"/>
-      <c r="K190" s="2" t="inlineStr">
-        <is>
-          <t>0,7НФ (евро): 42.50 ₽; 1,4НФ (полуторный): 56.77 ₽</t>
-        </is>
-      </c>
-      <c r="L190" s="2" t="n">
-        <v>51.4</v>
-      </c>
+      <c r="K190" s="2" t="inlineStr"/>
+      <c r="L190" s="2" t="n"/>
       <c r="M190" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N190" s="2" t="inlineStr"/>
       <c r="O190" s="2" t="inlineStr"/>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>Бежевый бриз</t>
+          <t>СВЕТЛЫЙ ВИНТАЖ Одинарный пустотелый М150 (F50 пустот 37%) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
         <is>
-          <t>Губский</t>
+          <t>Донской</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>pal-005</t>
+          <t>kla-038</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Палитра</t>
+          <t>Классика</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -12818,22 +12790,22 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Бромо</t>
+          <t>Светлый Крафт</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>Красный</t>
+          <t>желтый</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>бежевый</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>гладкий</t>
+          <t>фактурный</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -12842,46 +12814,36 @@
         </is>
       </c>
       <c r="I191" s="3" t="n">
-        <v>27.5</v>
+        <v>42</v>
       </c>
       <c r="J191" s="3" t="n"/>
-      <c r="K191" s="2" t="inlineStr">
-        <is>
-          <t>1,4НФ (полуторный): 35.15 ₽</t>
-        </is>
-      </c>
-      <c r="L191" s="2" t="n">
-        <v>51.4</v>
-      </c>
+      <c r="K191" s="2" t="inlineStr"/>
+      <c r="L191" s="2" t="n"/>
       <c r="M191" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N191" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N191" s="2" t="inlineStr"/>
       <c r="O191" s="2" t="inlineStr"/>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>Бромо</t>
+          <t>СВЕТЛЫЙ КРАФТ Лицевой Одинарный М150 (F50) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
         <is>
-          <t>Губский</t>
+          <t>Донской</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>pal-006</t>
+          <t>kla-039</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Палитра</t>
+          <t>Классика</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -12891,22 +12853,22 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Бромо Про</t>
+          <t>Светлый Терра</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>Красный</t>
+          <t>желтый</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>бежевый</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>гладкий</t>
+          <t>фактурный</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -12915,42 +12877,36 @@
         </is>
       </c>
       <c r="I192" s="3" t="n">
-        <v>29.5</v>
+        <v>42</v>
       </c>
       <c r="J192" s="3" t="n"/>
-      <c r="K192" s="2" t="inlineStr">
-        <is>
-          <t>0,9НФ: 29.50 ₽; 1,4НФ (полуторный): 37.15 ₽</t>
-        </is>
-      </c>
-      <c r="L192" s="2" t="n">
-        <v>51.4</v>
-      </c>
+      <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="2" t="n"/>
       <c r="M192" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N192" s="2" t="inlineStr"/>
       <c r="O192" s="2" t="inlineStr"/>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>Бромо Про</t>
+          <t>СВЕТЛЫЙ ТЕРРА Лицевой Одинарный М150 (F50) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
         <is>
-          <t>Губский</t>
+          <t>Донской</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>pal-007</t>
+          <t>kla-040</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Палитра</t>
+          <t>Классика</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -12960,12 +12916,12 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Габбро</t>
+          <t>Скала рельефный</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>Коричневый</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
@@ -12975,7 +12931,7 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>гладкий</t>
+          <t>рельефный</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
@@ -12984,44 +12940,36 @@
         </is>
       </c>
       <c r="I193" s="3" t="n">
-        <v>54.18</v>
+        <v>22.8</v>
       </c>
       <c r="J193" s="3" t="n"/>
-      <c r="K193" s="2" t="inlineStr">
-        <is>
-          <t>1,4НФ (полуторный): 66.22 ₽</t>
-        </is>
-      </c>
+      <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="n"/>
       <c r="M193" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N193" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N193" s="2" t="inlineStr"/>
       <c r="O193" s="2" t="inlineStr"/>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>Габбро</t>
+          <t>Скала Лицевой Одинарный Гладкий М150 (F50) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
         <is>
-          <t>Губский</t>
+          <t>Донской</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>pal-008</t>
+          <t>kla-041</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Палитра</t>
+          <t>Классика</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -13031,17 +12979,17 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Галерас Бавария</t>
+          <t>Солома</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>Красный</t>
+          <t>солома</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>микс (бавария)</t>
+          <t>бежевый</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
@@ -13055,46 +13003,44 @@
         </is>
       </c>
       <c r="I194" s="3" t="n">
-        <v>28.52</v>
+        <v>35.15</v>
       </c>
       <c r="J194" s="3" t="n"/>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>1,4НФ (полуторный): 37.19 ₽</t>
-        </is>
-      </c>
-      <c r="L194" s="2" t="n">
-        <v>51.4</v>
-      </c>
+          <t>1НФ (одинарный), марка М175: 35.15 ₽</t>
+        </is>
+      </c>
+      <c r="L194" s="2" t="n"/>
       <c r="M194" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N194" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="O194" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="N194" s="2" t="inlineStr"/>
+      <c r="O194" s="4" t="inlineStr">
+        <is>
+          <t>объединён вариант: "СОЛОМА" Лицевой Одинарный Гладкий М175 (F50) 416шт упак. пленкой</t>
+        </is>
+      </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>Галерас Бавария</t>
+          <t>"СОЛОМА" Лицевой Одинарный Гладкий М150 (F50) 480шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
         <is>
-          <t>Губский</t>
+          <t>Донской</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>pal-009</t>
+          <t>kla-042</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Палитра</t>
+          <t>Классика</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -13104,22 +13050,22 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Гранат</t>
+          <t>Солома Сахара</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>Бордовый</t>
+          <t>солома</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>бежевый</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>винтаж</t>
+          <t>сахара</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -13128,46 +13074,36 @@
         </is>
       </c>
       <c r="I195" s="3" t="n">
-        <v>43.56</v>
+        <v>35.15</v>
       </c>
       <c r="J195" s="3" t="n"/>
-      <c r="K195" s="2" t="inlineStr">
-        <is>
-          <t>1,4НФ (полуторный): 59.55 ₽</t>
-        </is>
-      </c>
-      <c r="L195" s="2" t="n">
-        <v>51.4</v>
-      </c>
+      <c r="K195" s="2" t="inlineStr"/>
+      <c r="L195" s="2" t="n"/>
       <c r="M195" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N195" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="N195" s="2" t="inlineStr"/>
       <c r="O195" s="2" t="inlineStr"/>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>Гранат</t>
+          <t>СОЛОМА САХАРА Лицевой Одинарный М175 (F75) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
         <is>
-          <t>Губский</t>
+          <t>Донской</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>pal-010</t>
+          <t>kla-043</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Палитра</t>
+          <t>Классика</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -13177,68 +13113,68 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Графит</t>
+          <t>Солома береста</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>Коричневый</t>
+          <t>солома</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>коричневый</t>
+          <t>бежевый</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>гладкий</t>
+          <t>береста</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>1НФ (одинарный)</t>
+          <t>1,4НФ (полуторный)</t>
         </is>
       </c>
       <c r="I196" s="3" t="n">
-        <v>55.04</v>
+        <v>44.25</v>
       </c>
       <c r="J196" s="3" t="n"/>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>1,4НФ (полуторный): 67.79 ₽</t>
+          <t>1НФ (одинарный): 35.15 ₽</t>
         </is>
       </c>
       <c r="L196" s="2" t="n"/>
       <c r="M196" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N196" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="O196" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="N196" s="2" t="inlineStr"/>
+      <c r="O196" s="4" t="inlineStr">
+        <is>
+          <t>объединён вариант: "СОЛОМА" Лицевой Одинарный "Коралл" М175 (F50) 416шт упак пленкой</t>
+        </is>
+      </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>Графит</t>
+          <t>"СОЛОМА" Лицевой Утолщенный М175 (F75) 320шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
         <is>
-          <t>Губский</t>
+          <t>Донской</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>pal-011</t>
+          <t>kla-044</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Палитра</t>
+          <t>Классика</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -13248,22 +13184,22 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Грей</t>
+          <t>Солома коралл</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>Серый</t>
+          <t>солома</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>серый</t>
+          <t>бежевый</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>руст</t>
+          <t>коралл</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -13272,46 +13208,40 @@
         </is>
       </c>
       <c r="I197" s="3" t="n">
-        <v>58.1</v>
+        <v>29.95</v>
       </c>
       <c r="J197" s="3" t="n"/>
-      <c r="K197" s="2" t="inlineStr">
-        <is>
-          <t>1,4НФ (полуторный): 71.36 ₽</t>
-        </is>
-      </c>
-      <c r="L197" s="2" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="M197" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N197" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="O197" s="2" t="inlineStr"/>
+      <c r="K197" s="2" t="inlineStr"/>
+      <c r="L197" s="2" t="n"/>
+      <c r="M197" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N197" s="2" t="inlineStr"/>
+      <c r="O197" s="4" t="inlineStr">
+        <is>
+          <t>нет фото</t>
+        </is>
+      </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>Грей</t>
+          <t>"СОЛОМА" Лицевой Одинарный "Коралл" М150 (F50) 480шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
         <is>
-          <t>Губский</t>
+          <t>Донской</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>pal-012</t>
+          <t>kla-045</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Палитра</t>
+          <t>Классика</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -13321,22 +13251,22 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Капучино</t>
+          <t>Тархан рельефный</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>Бежевый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>бежевый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>гладкий</t>
+          <t>рельефный</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -13345,46 +13275,36 @@
         </is>
       </c>
       <c r="I198" s="3" t="n">
-        <v>47.9</v>
+        <v>32.5</v>
       </c>
       <c r="J198" s="3" t="n"/>
-      <c r="K198" s="2" t="inlineStr">
-        <is>
-          <t>1,4НФ (полуторный): 61.67 ₽</t>
-        </is>
-      </c>
-      <c r="L198" s="2" t="n">
-        <v>51.4</v>
-      </c>
+      <c r="K198" s="2" t="inlineStr"/>
+      <c r="L198" s="2" t="n"/>
       <c r="M198" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N198" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N198" s="2" t="inlineStr"/>
       <c r="O198" s="2" t="inlineStr"/>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>Капучино</t>
+          <t>"ТАРХАН" Одинарный пустотелый М175 (F75) 416 шт.</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
         <is>
-          <t>Губский</t>
+          <t>Донской</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>pal-013</t>
+          <t>kla-046</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Палитра</t>
+          <t>Классика</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -13394,22 +13314,22 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Каракум</t>
+          <t>Темно-коричневый</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>Желтый</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>бежевый</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>руст</t>
+          <t>гладкий</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -13418,46 +13338,36 @@
         </is>
       </c>
       <c r="I199" s="3" t="n">
-        <v>47.9</v>
+        <v>48.25</v>
       </c>
       <c r="J199" s="3" t="n"/>
-      <c r="K199" s="2" t="inlineStr">
-        <is>
-          <t>0,9НФ: 47.90 ₽</t>
-        </is>
-      </c>
-      <c r="L199" s="2" t="n">
-        <v>51.4</v>
-      </c>
+      <c r="K199" s="2" t="inlineStr"/>
+      <c r="L199" s="2" t="n"/>
       <c r="M199" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N199" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N199" s="2" t="inlineStr"/>
       <c r="O199" s="2" t="inlineStr"/>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>Каракум</t>
+          <t>ТЕМНО-КОРИЧНЕВЫЙ Лицевой Одинарный М150 (F50) 416шт упак. пленкой</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
         <is>
-          <t>Губский</t>
+          <t>Донской</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>pal-014</t>
+          <t>kla-047</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Палитра</t>
+          <t>Классика</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -13467,12 +13377,12 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Каратау</t>
+          <t>Феррум</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>Красный</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
@@ -13482,50 +13392,40 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>гладкий</t>
+          <t>ручная формовка</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>1НФ (одинарный)</t>
+          <t>WDF</t>
         </is>
       </c>
       <c r="I200" s="3" t="n">
-        <v>29.54</v>
+        <v>68.2</v>
       </c>
       <c r="J200" s="3" t="n"/>
-      <c r="K200" s="2" t="inlineStr">
-        <is>
-          <t>1,4НФ (полуторный): 36.17 ₽</t>
-        </is>
-      </c>
-      <c r="L200" s="2" t="n">
-        <v>51.4</v>
-      </c>
+      <c r="K200" s="2" t="inlineStr"/>
+      <c r="L200" s="2" t="n"/>
       <c r="M200" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N200" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N200" s="2" t="inlineStr"/>
       <c r="O200" s="2" t="inlineStr"/>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>Каратау</t>
+          <t>"Феррум" Кирпич полнотелй ручной формовки М150 (F50 WDF ТУ) 556шт</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
         <is>
-          <t>Губский</t>
+          <t>Донской</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>pal-015</t>
+          <t>pal-001</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
@@ -13540,17 +13440,17 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Каратау Про 26</t>
+          <t>Абрикос</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>Красный</t>
+          <t>Розовый</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>персиковый</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
@@ -13564,19 +13464,19 @@
         </is>
       </c>
       <c r="I201" s="3" t="n">
-        <v>34.13</v>
+        <v>36.88</v>
       </c>
       <c r="J201" s="3" t="n"/>
       <c r="K201" s="2" t="inlineStr">
         <is>
-          <t>1,4НФ (полуторный): 42.29 ₽</t>
+          <t>0,7НФ (евро): 34.00 ₽; 0,9НФ: 36.88 ₽; 1,4НФ (полуторный): 47.78 ₽</t>
         </is>
       </c>
       <c r="L201" s="2" t="n">
         <v>51.4</v>
       </c>
       <c r="M201" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N201" s="2" t="inlineStr">
         <is>
@@ -13586,7 +13486,7 @@
       <c r="O201" s="2" t="inlineStr"/>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>Каратау Про 26</t>
+          <t>Абрикос</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -13598,7 +13498,7 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>pal-016</t>
+          <t>pal-002</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
@@ -13613,7 +13513,7 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Классика</t>
+          <t>Амбрим</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -13637,19 +13537,19 @@
         </is>
       </c>
       <c r="I202" s="3" t="n">
-        <v>25.64</v>
+        <v>26.48</v>
       </c>
       <c r="J202" s="3" t="n"/>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>0,7НФ (евро): 23.91 ₽; 0,9НФ: 25.64 ₽; 1,4НФ (полуторный): 32.56 ₽</t>
+          <t>1,4НФ (полуторный): 33.62 ₽</t>
         </is>
       </c>
       <c r="L202" s="2" t="n">
         <v>51.4</v>
       </c>
       <c r="M202" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N202" s="2" t="inlineStr">
         <is>
@@ -13659,7 +13559,7 @@
       <c r="O202" s="2" t="inlineStr"/>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>Классика</t>
+          <t>Амбрим</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -13671,7 +13571,7 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>pal-017</t>
+          <t>pal-003</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
@@ -13686,17 +13586,17 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Классика Про</t>
+          <t>Арес</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>Красный</t>
+          <t>Желтый</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>бежевый</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
@@ -13709,26 +13609,24 @@
           <t>1НФ (одинарный)</t>
         </is>
       </c>
-      <c r="I203" s="3" t="n">
-        <v>33.62</v>
-      </c>
+      <c r="I203" s="3" t="n"/>
       <c r="J203" s="3" t="n"/>
-      <c r="K203" s="2" t="inlineStr">
-        <is>
-          <t>0,9НФ: 33.62 ₽; 1НФ (одинарный): 33.62 ₽; 1,4НФ (полуторный): 41.78 ₽; 0,7НФ (евро): 31.00 ₽</t>
-        </is>
-      </c>
+      <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="2" t="n">
         <v>51.4</v>
       </c>
-      <c r="M203" s="2" t="n">
-        <v>8</v>
+      <c r="M203" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="N203" s="2" t="inlineStr"/>
-      <c r="O203" s="2" t="inlineStr"/>
+      <c r="O203" s="4" t="inlineStr">
+        <is>
+          <t>нет фото</t>
+        </is>
+      </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>Классика Про</t>
+          <t>Арес</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -13740,7 +13638,7 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>pal-018</t>
+          <t>pal-004</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -13755,22 +13653,22 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Кора Кедра</t>
+          <t>Бежевая Кора</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>Красный</t>
+          <t>Бежевый</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>бежевый</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>руст</t>
+          <t>кора</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -13779,29 +13677,25 @@
         </is>
       </c>
       <c r="I204" s="3" t="n">
-        <v>30.05</v>
+        <v>45.86</v>
       </c>
       <c r="J204" s="3" t="n"/>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>0,9НФ: 30.05 ₽; 1,4НФ (полуторный): 38.21 ₽</t>
+          <t>0,7НФ (евро): 42.50 ₽; 1,4НФ (полуторный): 56.77 ₽</t>
         </is>
       </c>
       <c r="L204" s="2" t="n">
         <v>51.4</v>
       </c>
       <c r="M204" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N204" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="N204" s="2" t="inlineStr"/>
       <c r="O204" s="2" t="inlineStr"/>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>Кора Кедра</t>
+          <t>Бежевая кора</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -13813,7 +13707,7 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>pal-019</t>
+          <t>pal-005</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
@@ -13828,22 +13722,22 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Коралл</t>
+          <t>Бежевый Бриз</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>Бордовый</t>
+          <t>Бежевый</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>персиковый</t>
+          <t>бежевый</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>коралл</t>
+          <t>бриз</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -13852,29 +13746,25 @@
         </is>
       </c>
       <c r="I205" s="3" t="n">
-        <v>49.94</v>
+        <v>45.86</v>
       </c>
       <c r="J205" s="3" t="n"/>
       <c r="K205" s="2" t="inlineStr">
         <is>
-          <t>1,4НФ (полуторный): 64.22 ₽</t>
+          <t>0,7НФ (евро): 42.50 ₽; 1,4НФ (полуторный): 56.77 ₽</t>
         </is>
       </c>
       <c r="L205" s="2" t="n">
         <v>51.4</v>
       </c>
       <c r="M205" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N205" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N205" s="2" t="inlineStr"/>
       <c r="O205" s="2" t="inlineStr"/>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>Коралл</t>
+          <t>Бежевый бриз</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -13886,7 +13776,7 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>pal-020</t>
+          <t>pal-006</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
@@ -13901,17 +13791,17 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Корица</t>
+          <t>Бромо</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>Коричневый</t>
+          <t>Красный</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>коричневый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
@@ -13925,25 +13815,29 @@
         </is>
       </c>
       <c r="I206" s="3" t="n">
-        <v>43.49</v>
+        <v>27.5</v>
       </c>
       <c r="J206" s="3" t="n"/>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>1,4НФ (полуторный): 56.49 ₽</t>
+          <t>1,4НФ (полуторный): 35.15 ₽</t>
         </is>
       </c>
       <c r="L206" s="2" t="n">
         <v>51.4</v>
       </c>
       <c r="M206" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N206" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="N206" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="O206" s="2" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>Корица</t>
+          <t>Бромо</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -13955,7 +13849,7 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>pal-021</t>
+          <t>pal-007</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
@@ -13970,22 +13864,22 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Коста</t>
+          <t>Бромо Про</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>Бежевый</t>
+          <t>Красный</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>бежевый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>руст</t>
+          <t>гладкий</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -13994,29 +13888,25 @@
         </is>
       </c>
       <c r="I207" s="3" t="n">
-        <v>44.84</v>
+        <v>29.5</v>
       </c>
       <c r="J207" s="3" t="n"/>
       <c r="K207" s="2" t="inlineStr">
         <is>
-          <t>1,4НФ (полуторный): 55.04 ₽</t>
+          <t>0,9НФ: 29.50 ₽; 1,4НФ (полуторный): 37.15 ₽</t>
         </is>
       </c>
       <c r="L207" s="2" t="n">
         <v>51.4</v>
       </c>
       <c r="M207" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N207" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="N207" s="2" t="inlineStr"/>
       <c r="O207" s="2" t="inlineStr"/>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>Коста</t>
+          <t>Бромо Про</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
@@ -14028,7 +13918,7 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>pal-022</t>
+          <t>pal-008</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -14043,22 +13933,22 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Красная Кора</t>
+          <t>Габбро</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>Красный</t>
+          <t>Коричневый</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>руст</t>
+          <t>гладкий</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -14067,19 +13957,17 @@
         </is>
       </c>
       <c r="I208" s="3" t="n">
-        <v>25.64</v>
+        <v>54.18</v>
       </c>
       <c r="J208" s="3" t="n"/>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>0,7НФ (евро): 23.91 ₽; 0,9НФ: 25.64 ₽; 1,4НФ (полуторный): 32.56 ₽</t>
-        </is>
-      </c>
-      <c r="L208" s="2" t="n">
-        <v>51.4</v>
-      </c>
+          <t>1,4НФ (полуторный): 66.22 ₽</t>
+        </is>
+      </c>
+      <c r="L208" s="2" t="n"/>
       <c r="M208" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N208" s="2" t="inlineStr">
         <is>
@@ -14089,7 +13977,7 @@
       <c r="O208" s="2" t="inlineStr"/>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>Красная Кора</t>
+          <t>Габбро</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
@@ -14101,7 +13989,7 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>pal-023</t>
+          <t>pal-009</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
@@ -14116,7 +14004,7 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Красный Бриз</t>
+          <t>Галерас Бавария</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -14126,12 +14014,12 @@
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>микс (бавария)</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>рельефный</t>
+          <t>гладкий</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
@@ -14140,19 +14028,19 @@
         </is>
       </c>
       <c r="I209" s="3" t="n">
-        <v>25.64</v>
+        <v>28.52</v>
       </c>
       <c r="J209" s="3" t="n"/>
       <c r="K209" s="2" t="inlineStr">
         <is>
-          <t>0,7НФ (евро): 23.91 ₽; 1,4НФ (полуторный): 32.56 ₽; 0,9НФ: 25.64 ₽</t>
+          <t>1,4НФ (полуторный): 37.19 ₽</t>
         </is>
       </c>
       <c r="L209" s="2" t="n">
         <v>51.4</v>
       </c>
       <c r="M209" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N209" s="2" t="inlineStr">
         <is>
@@ -14162,7 +14050,7 @@
       <c r="O209" s="2" t="inlineStr"/>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>Красный Бриз</t>
+          <t>Галерас Бавария</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -14174,7 +14062,7 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>pal-024</t>
+          <t>pal-010</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -14189,12 +14077,12 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Магма</t>
+          <t>Гранат</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>Красный</t>
+          <t>Бордовый</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
@@ -14204,7 +14092,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>руст</t>
+          <t>винтаж</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -14213,19 +14101,19 @@
         </is>
       </c>
       <c r="I210" s="3" t="n">
-        <v>28.52</v>
+        <v>43.56</v>
       </c>
       <c r="J210" s="3" t="n"/>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>0,7НФ (евро): 26.50 ₽; 1,4НФ (полуторный): 35.66 ₽</t>
+          <t>1,4НФ (полуторный): 59.55 ₽</t>
         </is>
       </c>
       <c r="L210" s="2" t="n">
         <v>51.4</v>
       </c>
       <c r="M210" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N210" s="2" t="inlineStr">
         <is>
@@ -14235,7 +14123,7 @@
       <c r="O210" s="2" t="inlineStr"/>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>Магма</t>
+          <t>Гранат</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr">
@@ -14247,7 +14135,7 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>pal-025</t>
+          <t>pal-011</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
@@ -14262,17 +14150,17 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Магма Про</t>
+          <t>Графит</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>Красный</t>
+          <t>Коричневый</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
@@ -14286,19 +14174,17 @@
         </is>
       </c>
       <c r="I211" s="3" t="n">
-        <v>32.6</v>
+        <v>55.04</v>
       </c>
       <c r="J211" s="3" t="n"/>
       <c r="K211" s="2" t="inlineStr">
         <is>
-          <t>0,7НФ (евро): 30.00 ₽; 1,4НФ (полуторный): 40.76 ₽</t>
-        </is>
-      </c>
-      <c r="L211" s="2" t="n">
-        <v>51.4</v>
-      </c>
+          <t>1,4НФ (полуторный): 67.79 ₽</t>
+        </is>
+      </c>
+      <c r="L211" s="2" t="n"/>
       <c r="M211" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N211" s="2" t="inlineStr">
         <is>
@@ -14308,7 +14194,7 @@
       <c r="O211" s="2" t="inlineStr"/>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>Магма Про</t>
+          <t>Графит</t>
         </is>
       </c>
       <c r="Q211" s="2" t="inlineStr">
@@ -14320,7 +14206,7 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>pal-026</t>
+          <t>pal-012</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -14335,22 +14221,22 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Малахит</t>
+          <t>Грей</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>Зеленый</t>
+          <t>Серый</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>зелёный</t>
+          <t>серый</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>гладкий</t>
+          <t>руст</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -14359,15 +14245,19 @@
         </is>
       </c>
       <c r="I212" s="3" t="n">
-        <v>88.7</v>
+        <v>58.1</v>
       </c>
       <c r="J212" s="3" t="n"/>
-      <c r="K212" s="2" t="inlineStr"/>
+      <c r="K212" s="2" t="inlineStr">
+        <is>
+          <t>1,4НФ (полуторный): 71.36 ₽</t>
+        </is>
+      </c>
       <c r="L212" s="2" t="n">
         <v>51.4</v>
       </c>
       <c r="M212" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N212" s="2" t="inlineStr">
         <is>
@@ -14377,7 +14267,7 @@
       <c r="O212" s="2" t="inlineStr"/>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>Малахит</t>
+          <t>Грей</t>
         </is>
       </c>
       <c r="Q212" s="2" t="inlineStr">
@@ -14389,7 +14279,7 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>pal-027</t>
+          <t>pal-013</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
@@ -14404,17 +14294,17 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Мускат</t>
+          <t>Капучино</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>Коричневый</t>
+          <t>Бежевый</t>
         </is>
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t>коричневый</t>
+          <t>бежевый</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
@@ -14428,23 +14318,29 @@
         </is>
       </c>
       <c r="I213" s="3" t="n">
-        <v>49.57</v>
+        <v>47.9</v>
       </c>
       <c r="J213" s="3" t="n"/>
       <c r="K213" s="2" t="inlineStr">
         <is>
-          <t>0,7НФ (евро): 45.50 ₽; 1,4НФ (полуторный): 62.83 ₽</t>
-        </is>
-      </c>
-      <c r="L213" s="2" t="n"/>
+          <t>1,4НФ (полуторный): 61.67 ₽</t>
+        </is>
+      </c>
+      <c r="L213" s="2" t="n">
+        <v>51.4</v>
+      </c>
       <c r="M213" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N213" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="N213" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="O213" s="2" t="inlineStr"/>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>Мускат</t>
+          <t>Капучино</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -14456,7 +14352,7 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>pal-028</t>
+          <t>pal-014</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -14471,12 +14367,12 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Памир</t>
+          <t>Каракум</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>Бежевый</t>
+          <t>Желтый</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr">
@@ -14486,7 +14382,7 @@
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>гладкий</t>
+          <t>руст</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
@@ -14500,14 +14396,14 @@
       <c r="J214" s="3" t="n"/>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>0,9НФ: 47.90 ₽; 1,4НФ (полуторный): 65.24 ₽</t>
+          <t>0,9НФ: 47.90 ₽</t>
         </is>
       </c>
       <c r="L214" s="2" t="n">
         <v>51.4</v>
       </c>
       <c r="M214" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N214" s="2" t="inlineStr">
         <is>
@@ -14517,7 +14413,7 @@
       <c r="O214" s="2" t="inlineStr"/>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>Памир</t>
+          <t>Каракум</t>
         </is>
       </c>
       <c r="Q214" s="2" t="inlineStr">
@@ -14529,7 +14425,7 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>pal-029</t>
+          <t>pal-015</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -14544,17 +14440,17 @@
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Песчаная Дюна</t>
+          <t>Каратау</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>Розовый</t>
+          <t>Красный</t>
         </is>
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t>бежевый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
@@ -14568,19 +14464,19 @@
         </is>
       </c>
       <c r="I215" s="3" t="n">
-        <v>39.74</v>
+        <v>29.54</v>
       </c>
       <c r="J215" s="3" t="n"/>
       <c r="K215" s="2" t="inlineStr">
         <is>
-          <t>1,4НФ (полуторный): 52.49 ₽</t>
+          <t>1,4НФ (полуторный): 36.17 ₽</t>
         </is>
       </c>
       <c r="L215" s="2" t="n">
         <v>51.4</v>
       </c>
       <c r="M215" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N215" s="2" t="inlineStr">
         <is>
@@ -14590,7 +14486,7 @@
       <c r="O215" s="2" t="inlineStr"/>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>Песчаная дюна</t>
+          <t>Каратау</t>
         </is>
       </c>
       <c r="Q215" s="2" t="inlineStr">
@@ -14602,7 +14498,7 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>pal-030</t>
+          <t>pal-016</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -14617,22 +14513,22 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Пшеница</t>
+          <t>Каратау Про 26</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>Желтый</t>
+          <t>Красный</t>
         </is>
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>бежевый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>руст</t>
+          <t>гладкий</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -14641,25 +14537,29 @@
         </is>
       </c>
       <c r="I216" s="3" t="n">
-        <v>46.93</v>
+        <v>34.13</v>
       </c>
       <c r="J216" s="3" t="n"/>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>1,4НФ (полуторный): 64.80 ₽</t>
+          <t>1,4НФ (полуторный): 42.29 ₽</t>
         </is>
       </c>
       <c r="L216" s="2" t="n">
         <v>51.4</v>
       </c>
       <c r="M216" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N216" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="N216" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="O216" s="2" t="inlineStr"/>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>Пшеница</t>
+          <t>Каратау Про 26</t>
         </is>
       </c>
       <c r="Q216" s="2" t="inlineStr">
@@ -14671,7 +14571,7 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>pal-031</t>
+          <t>pal-017</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
@@ -14686,17 +14586,17 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Рейнир 10.24</t>
+          <t>Классика</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>Коричневый</t>
+          <t>Красный</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>коричневый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
@@ -14710,17 +14610,19 @@
         </is>
       </c>
       <c r="I217" s="3" t="n">
-        <v>58.04</v>
+        <v>25.64</v>
       </c>
       <c r="J217" s="3" t="n"/>
       <c r="K217" s="2" t="inlineStr">
         <is>
-          <t>1,4НФ (полуторный): 70.79 ₽</t>
-        </is>
-      </c>
-      <c r="L217" s="2" t="n"/>
+          <t>0,7НФ (евро): 23.91 ₽; 0,9НФ: 25.64 ₽; 1,4НФ (полуторный): 32.56 ₽</t>
+        </is>
+      </c>
+      <c r="L217" s="2" t="n">
+        <v>51.4</v>
+      </c>
       <c r="M217" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N217" s="2" t="inlineStr">
         <is>
@@ -14730,7 +14632,7 @@
       <c r="O217" s="2" t="inlineStr"/>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>Рейнир 10.24</t>
+          <t>Классика</t>
         </is>
       </c>
       <c r="Q217" s="2" t="inlineStr">
@@ -14742,7 +14644,7 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>pal-032</t>
+          <t>pal-018</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -14757,22 +14659,22 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Розовая Кора</t>
+          <t>Классика Про</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>Розовый</t>
+          <t>Красный</t>
         </is>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t>персиковый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>антик</t>
+          <t>гладкий</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -14781,25 +14683,25 @@
         </is>
       </c>
       <c r="I218" s="3" t="n">
-        <v>36.88</v>
+        <v>33.62</v>
       </c>
       <c r="J218" s="3" t="n"/>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>0,7НФ (евро): 34.00 ₽; 1,4НФ (полуторный): 47.78 ₽</t>
+          <t>0,9НФ: 33.62 ₽; 1НФ (одинарный): 33.62 ₽; 1,4НФ (полуторный): 41.78 ₽; 0,7НФ (евро): 31.00 ₽</t>
         </is>
       </c>
       <c r="L218" s="2" t="n">
         <v>51.4</v>
       </c>
       <c r="M218" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N218" s="2" t="inlineStr"/>
       <c r="O218" s="2" t="inlineStr"/>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>Розовая кора</t>
+          <t>Классика Про</t>
         </is>
       </c>
       <c r="Q218" s="2" t="inlineStr">
@@ -14811,7 +14713,7 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>pal-033</t>
+          <t>pal-019</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
@@ -14826,22 +14728,22 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Розовый Бриз</t>
+          <t>Кора Кедра</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>Розовый</t>
+          <t>Красный</t>
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>персиковый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>бриз</t>
+          <t>руст</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
@@ -14850,25 +14752,29 @@
         </is>
       </c>
       <c r="I219" s="3" t="n">
-        <v>36.88</v>
+        <v>30.05</v>
       </c>
       <c r="J219" s="3" t="n"/>
       <c r="K219" s="2" t="inlineStr">
         <is>
-          <t>0,7НФ (евро): 34.00 ₽; 1,4НФ (полуторный): 47.78 ₽</t>
+          <t>0,9НФ: 30.05 ₽; 1,4НФ (полуторный): 38.21 ₽</t>
         </is>
       </c>
       <c r="L219" s="2" t="n">
         <v>51.4</v>
       </c>
       <c r="M219" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N219" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="N219" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="O219" s="2" t="inlineStr"/>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>Розовый бриз</t>
+          <t>Кора Кедра</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -14880,7 +14786,7 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>pal-034</t>
+          <t>pal-020</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -14895,22 +14801,22 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Розовый Мрамор</t>
+          <t>Коралл</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>Бежевый</t>
+          <t>Бордовый</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>серый</t>
+          <t>персиковый</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>руст</t>
+          <t>коралл</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -14919,19 +14825,19 @@
         </is>
       </c>
       <c r="I220" s="3" t="n">
-        <v>44.84</v>
+        <v>49.94</v>
       </c>
       <c r="J220" s="3" t="n"/>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>0,9НФ: 44.84 ₽; 1,4НФ (полуторный): 55.04 ₽</t>
+          <t>1,4НФ (полуторный): 64.22 ₽</t>
         </is>
       </c>
       <c r="L220" s="2" t="n">
         <v>51.4</v>
       </c>
       <c r="M220" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N220" s="2" t="inlineStr">
         <is>
@@ -14941,7 +14847,7 @@
       <c r="O220" s="2" t="inlineStr"/>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>Розовый мрамор</t>
+          <t>Коралл</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -14953,7 +14859,7 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>pal-035</t>
+          <t>pal-021</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -14968,17 +14874,17 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>Сафари</t>
+          <t>Корица</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>Бежевый</t>
+          <t>Коричневый</t>
         </is>
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>бежевый</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
@@ -14992,29 +14898,25 @@
         </is>
       </c>
       <c r="I221" s="3" t="n">
-        <v>45.86</v>
+        <v>43.49</v>
       </c>
       <c r="J221" s="3" t="n"/>
       <c r="K221" s="2" t="inlineStr">
         <is>
-          <t>0,7НФ (евро): 42.50 ₽; 1,4НФ (полуторный): 56.77 ₽</t>
+          <t>1,4НФ (полуторный): 56.49 ₽</t>
         </is>
       </c>
       <c r="L221" s="2" t="n">
         <v>51.4</v>
       </c>
       <c r="M221" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N221" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="N221" s="2" t="inlineStr"/>
       <c r="O221" s="2" t="inlineStr"/>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>Сафари</t>
+          <t>Корица</t>
         </is>
       </c>
       <c r="Q221" s="2" t="inlineStr">
@@ -15026,7 +14928,7 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>pal-036</t>
+          <t>pal-022</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -15041,12 +14943,12 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Сахара</t>
+          <t>Коста</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>Красный</t>
+          <t>Бежевый</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
@@ -15065,19 +14967,19 @@
         </is>
       </c>
       <c r="I222" s="3" t="n">
-        <v>25.64</v>
+        <v>44.84</v>
       </c>
       <c r="J222" s="3" t="n"/>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>1,4НФ (полуторный): 33.29 ₽</t>
+          <t>1,4НФ (полуторный): 55.04 ₽</t>
         </is>
       </c>
       <c r="L222" s="2" t="n">
         <v>51.4</v>
       </c>
       <c r="M222" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N222" s="2" t="inlineStr">
         <is>
@@ -15087,7 +14989,7 @@
       <c r="O222" s="2" t="inlineStr"/>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>Сахара</t>
+          <t>Коста</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -15099,7 +15001,7 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>pal-037</t>
+          <t>pal-023</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -15114,22 +15016,22 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Светло-бежевый</t>
+          <t>Красная Кора</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>Бежевый</t>
+          <t>Красный</t>
         </is>
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>бежевый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>гладкий</t>
+          <t>руст</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
@@ -15138,19 +15040,19 @@
         </is>
       </c>
       <c r="I223" s="3" t="n">
-        <v>41.74</v>
+        <v>25.64</v>
       </c>
       <c r="J223" s="3" t="n"/>
       <c r="K223" s="2" t="inlineStr">
         <is>
-          <t>0,7НФ (евро): 38.55 ₽; 0,9НФ: 41.74 ₽; 1,4НФ (полуторный): 50.92 ₽</t>
+          <t>0,7НФ (евро): 23.91 ₽; 0,9НФ: 25.64 ₽; 1,4НФ (полуторный): 32.56 ₽</t>
         </is>
       </c>
       <c r="L223" s="2" t="n">
         <v>51.4</v>
       </c>
       <c r="M223" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N223" s="2" t="inlineStr">
         <is>
@@ -15160,7 +15062,7 @@
       <c r="O223" s="2" t="inlineStr"/>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>Светло-бежевый</t>
+          <t>Красная Кора</t>
         </is>
       </c>
       <c r="Q223" s="2" t="inlineStr">
@@ -15172,7 +15074,7 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>pal-038</t>
+          <t>pal-024</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -15187,12 +15089,12 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Светло-гранатовый</t>
+          <t>Красный Бриз</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>Бордовый</t>
+          <t>Красный</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr">
@@ -15202,7 +15104,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>гладкий</t>
+          <t>рельефный</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -15211,19 +15113,19 @@
         </is>
       </c>
       <c r="I224" s="3" t="n">
-        <v>40.7</v>
+        <v>25.64</v>
       </c>
       <c r="J224" s="3" t="n"/>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>1,4НФ (полуторный): 51.41 ₽</t>
+          <t>0,7НФ (евро): 23.91 ₽; 1,4НФ (полуторный): 32.56 ₽; 0,9НФ: 25.64 ₽</t>
         </is>
       </c>
       <c r="L224" s="2" t="n">
         <v>51.4</v>
       </c>
       <c r="M224" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N224" s="2" t="inlineStr">
         <is>
@@ -15233,7 +15135,7 @@
       <c r="O224" s="2" t="inlineStr"/>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>Светло-гранатовый</t>
+          <t>Красный Бриз</t>
         </is>
       </c>
       <c r="Q224" s="2" t="inlineStr">
@@ -15245,7 +15147,7 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>pal-039</t>
+          <t>pal-025</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -15260,22 +15162,22 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Светло-зеленый</t>
+          <t>Магма</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>Зеленый</t>
+          <t>Красный</t>
         </is>
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>зелёный</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>гладкий</t>
+          <t>руст</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -15284,15 +15186,19 @@
         </is>
       </c>
       <c r="I225" s="3" t="n">
-        <v>81.56</v>
+        <v>28.52</v>
       </c>
       <c r="J225" s="3" t="n"/>
-      <c r="K225" s="2" t="inlineStr"/>
+      <c r="K225" s="2" t="inlineStr">
+        <is>
+          <t>0,7НФ (евро): 26.50 ₽; 1,4НФ (полуторный): 35.66 ₽</t>
+        </is>
+      </c>
       <c r="L225" s="2" t="n">
         <v>51.4</v>
       </c>
       <c r="M225" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N225" s="2" t="inlineStr">
         <is>
@@ -15302,7 +15208,7 @@
       <c r="O225" s="2" t="inlineStr"/>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>Светло-зеленый</t>
+          <t>Магма</t>
         </is>
       </c>
       <c r="Q225" s="2" t="inlineStr">
@@ -15314,7 +15220,7 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>pal-040</t>
+          <t>pal-026</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -15329,17 +15235,17 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Светло-серый</t>
+          <t>Магма Про</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>Серый</t>
+          <t>Красный</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>серый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
@@ -15353,19 +15259,19 @@
         </is>
       </c>
       <c r="I226" s="3" t="n">
-        <v>56.57</v>
+        <v>32.6</v>
       </c>
       <c r="J226" s="3" t="n"/>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>1,4НФ (полуторный): 70.85 ₽</t>
+          <t>0,7НФ (евро): 30.00 ₽; 1,4НФ (полуторный): 40.76 ₽</t>
         </is>
       </c>
       <c r="L226" s="2" t="n">
         <v>51.4</v>
       </c>
       <c r="M226" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N226" s="2" t="inlineStr">
         <is>
@@ -15375,7 +15281,7 @@
       <c r="O226" s="2" t="inlineStr"/>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>Светло-серый</t>
+          <t>Магма Про</t>
         </is>
       </c>
       <c r="Q226" s="2" t="inlineStr">
@@ -15387,7 +15293,7 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>pal-041</t>
+          <t>pal-027</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -15402,17 +15308,17 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Сиена Луч 1024</t>
+          <t>Малахит</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>Коричневый</t>
+          <t>Зеленый</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>коричневый</t>
+          <t>зелёный</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
@@ -15426,17 +15332,15 @@
         </is>
       </c>
       <c r="I227" s="3" t="n">
-        <v>39.74</v>
+        <v>88.7</v>
       </c>
       <c r="J227" s="3" t="n"/>
-      <c r="K227" s="2" t="inlineStr">
-        <is>
-          <t>1,4НФ (полуторный): 48.92 ₽</t>
-        </is>
-      </c>
-      <c r="L227" s="2" t="n"/>
+      <c r="K227" s="2" t="inlineStr"/>
+      <c r="L227" s="2" t="n">
+        <v>51.4</v>
+      </c>
       <c r="M227" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N227" s="2" t="inlineStr">
         <is>
@@ -15446,7 +15350,7 @@
       <c r="O227" s="2" t="inlineStr"/>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>Сиена луч 1024</t>
+          <t>Малахит</t>
         </is>
       </c>
       <c r="Q227" s="2" t="inlineStr">
@@ -15458,7 +15362,7 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>pal-042</t>
+          <t>pal-028</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -15473,7 +15377,7 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Старый Город Бромо Про 26</t>
+          <t>Марс 01</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -15496,20 +15400,24 @@
           <t>1НФ (одинарный)</t>
         </is>
       </c>
-      <c r="I228" s="3" t="n">
-        <v>28.5</v>
-      </c>
+      <c r="I228" s="3" t="n"/>
       <c r="J228" s="3" t="n"/>
       <c r="K228" s="2" t="inlineStr"/>
-      <c r="L228" s="2" t="n"/>
-      <c r="M228" s="2" t="n">
-        <v>8</v>
+      <c r="L228" s="2" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="M228" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="N228" s="2" t="inlineStr"/>
-      <c r="O228" s="2" t="inlineStr"/>
+      <c r="O228" s="4" t="inlineStr">
+        <is>
+          <t>нет фото</t>
+        </is>
+      </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>Старый город Бромо про 26</t>
+          <t>Марс 01 УС</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -15521,7 +15429,7 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>pal-043</t>
+          <t>pal-029</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -15536,17 +15444,17 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Старый Город Грей-по Рф</t>
+          <t>Марс 02</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>Серый</t>
+          <t>Красный</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>серый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
@@ -15559,20 +15467,24 @@
           <t>1НФ (одинарный)</t>
         </is>
       </c>
-      <c r="I229" s="3" t="n">
-        <v>61</v>
-      </c>
+      <c r="I229" s="3" t="n"/>
       <c r="J229" s="3" t="n"/>
       <c r="K229" s="2" t="inlineStr"/>
-      <c r="L229" s="2" t="n"/>
-      <c r="M229" s="2" t="n">
-        <v>8</v>
+      <c r="L229" s="2" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="M229" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="N229" s="2" t="inlineStr"/>
-      <c r="O229" s="2" t="inlineStr"/>
+      <c r="O229" s="4" t="inlineStr">
+        <is>
+          <t>нет фото</t>
+        </is>
+      </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>Старый город грей-по рф</t>
+          <t>Марс 02 УС</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -15584,7 +15496,7 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>pal-044</t>
+          <t>pal-030</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -15599,22 +15511,22 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Старый Город Графит</t>
+          <t>Марс 03</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>Коричневый</t>
+          <t>Красный</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>коричневый</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>старый город</t>
+          <t>гладкий</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -15622,24 +15534,24 @@
           <t>1НФ (одинарный)</t>
         </is>
       </c>
-      <c r="I230" s="3" t="n">
-        <v>55.04</v>
-      </c>
+      <c r="I230" s="3" t="n"/>
       <c r="J230" s="3" t="n"/>
-      <c r="K230" s="2" t="inlineStr">
-        <is>
-          <t>1,4НФ (полуторный): 67.79 ₽</t>
-        </is>
-      </c>
-      <c r="L230" s="2" t="n"/>
-      <c r="M230" s="2" t="n">
-        <v>8</v>
+      <c r="K230" s="2" t="inlineStr"/>
+      <c r="L230" s="2" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="M230" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="N230" s="2" t="inlineStr"/>
-      <c r="O230" s="2" t="inlineStr"/>
+      <c r="O230" s="4" t="inlineStr">
+        <is>
+          <t>нет фото</t>
+        </is>
+      </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>Старый город графит</t>
+          <t>Марс 03 УС</t>
         </is>
       </c>
       <c r="Q230" s="2" t="inlineStr">
@@ -15651,7 +15563,7 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>pal-045</t>
+          <t>pal-031</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -15666,22 +15578,22 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Старый Город Грей</t>
+          <t>Мускат</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>Серый</t>
+          <t>Коричневый</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>серый</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>старый город</t>
+          <t>гладкий</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -15690,23 +15602,23 @@
         </is>
       </c>
       <c r="I231" s="3" t="n">
-        <v>58.1</v>
+        <v>49.57</v>
       </c>
       <c r="J231" s="3" t="n"/>
       <c r="K231" s="2" t="inlineStr">
         <is>
-          <t>1,4НФ (полуторный): 71.36 ₽</t>
+          <t>0,7НФ (евро): 45.50 ₽; 1,4НФ (полуторный): 62.83 ₽</t>
         </is>
       </c>
       <c r="L231" s="2" t="n"/>
       <c r="M231" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N231" s="2" t="inlineStr"/>
       <c r="O231" s="2" t="inlineStr"/>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>Старый город грей</t>
+          <t>Мускат</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -15718,7 +15630,7 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>pal-046</t>
+          <t>pal-032</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -15733,22 +15645,22 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Старый Город Терра</t>
+          <t>Памир</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>Красный</t>
+          <t>Бежевый</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>бежевый</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>старый город</t>
+          <t>гладкий</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -15757,25 +15669,29 @@
         </is>
       </c>
       <c r="I232" s="3" t="n">
-        <v>29.54</v>
+        <v>47.9</v>
       </c>
       <c r="J232" s="3" t="n"/>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>1,4НФ (полуторный): 36.17 ₽</t>
+          <t>0,9НФ: 47.90 ₽; 1,4НФ (полуторный): 65.24 ₽</t>
         </is>
       </c>
       <c r="L232" s="2" t="n">
         <v>51.4</v>
       </c>
       <c r="M232" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N232" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="N232" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="O232" s="2" t="inlineStr"/>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>Старый город Терра</t>
+          <t>Памир</t>
         </is>
       </c>
       <c r="Q232" s="2" t="inlineStr">
@@ -15787,7 +15703,7 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>pal-047</t>
+          <t>pal-033</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -15802,22 +15718,22 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Старый Город Терра Про</t>
+          <t>Песчаная Дюна</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>Красный</t>
+          <t>Розовый</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>бежевый</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>старый город</t>
+          <t>гладкий</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -15826,19 +15742,19 @@
         </is>
       </c>
       <c r="I233" s="3" t="n">
-        <v>31.58</v>
+        <v>39.74</v>
       </c>
       <c r="J233" s="3" t="n"/>
       <c r="K233" s="2" t="inlineStr">
         <is>
-          <t>1,4НФ (полуторный): 38.72 ₽</t>
+          <t>1,4НФ (полуторный): 52.49 ₽</t>
         </is>
       </c>
       <c r="L233" s="2" t="n">
         <v>51.4</v>
       </c>
       <c r="M233" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N233" s="2" t="inlineStr">
         <is>
@@ -15848,7 +15764,7 @@
       <c r="O233" s="2" t="inlineStr"/>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>Старый город Терра Про</t>
+          <t>Песчаная дюна</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -15860,7 +15776,7 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>pal-048</t>
+          <t>pal-034</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -15875,22 +15791,22 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Старый Город Терра Про-по Рф</t>
+          <t>Пшеница</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>Красный</t>
+          <t>Желтый</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>бежевый</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>старый город</t>
+          <t>руст</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -15899,21 +15815,25 @@
         </is>
       </c>
       <c r="I234" s="3" t="n">
-        <v>52</v>
+        <v>46.93</v>
       </c>
       <c r="J234" s="3" t="n"/>
-      <c r="K234" s="2" t="inlineStr"/>
+      <c r="K234" s="2" t="inlineStr">
+        <is>
+          <t>1,4НФ (полуторный): 64.80 ₽</t>
+        </is>
+      </c>
       <c r="L234" s="2" t="n">
         <v>51.4</v>
       </c>
       <c r="M234" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N234" s="2" t="inlineStr"/>
       <c r="O234" s="2" t="inlineStr"/>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>Старый Город Терра Про-по рф</t>
+          <t>Пшеница</t>
         </is>
       </c>
       <c r="Q234" s="2" t="inlineStr">
@@ -15925,7 +15845,7 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>pal-049</t>
+          <t>pal-035</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -15940,22 +15860,22 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Старый Город Терра-по Рф</t>
+          <t>Рейнир 10.24</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>Красный</t>
+          <t>Коричневый</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>старый город</t>
+          <t>гладкий</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -15964,21 +15884,27 @@
         </is>
       </c>
       <c r="I235" s="3" t="n">
-        <v>51</v>
+        <v>58.04</v>
       </c>
       <c r="J235" s="3" t="n"/>
-      <c r="K235" s="2" t="inlineStr"/>
-      <c r="L235" s="2" t="n">
-        <v>51.4</v>
-      </c>
+      <c r="K235" s="2" t="inlineStr">
+        <is>
+          <t>1,4НФ (полуторный): 70.79 ₽</t>
+        </is>
+      </c>
+      <c r="L235" s="2" t="n"/>
       <c r="M235" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N235" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="N235" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="O235" s="2" t="inlineStr"/>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>Старый Город Терра-по рф</t>
+          <t>Рейнир 10.24</t>
         </is>
       </c>
       <c r="Q235" s="2" t="inlineStr">
@@ -15990,7 +15916,7 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>pal-050</t>
+          <t>pal-036</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -16005,22 +15931,22 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Фишт</t>
+          <t>Розовая Кора</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>Бежевый</t>
+          <t>Розовый</t>
         </is>
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>бежевый</t>
+          <t>персиковый</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>гладкий</t>
+          <t>антик</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
@@ -16029,25 +15955,25 @@
         </is>
       </c>
       <c r="I236" s="3" t="n">
-        <v>44.84</v>
+        <v>36.88</v>
       </c>
       <c r="J236" s="3" t="n"/>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>1,4НФ (полуторный): 55.04 ₽</t>
+          <t>0,7НФ (евро): 34.00 ₽; 1,4НФ (полуторный): 47.78 ₽</t>
         </is>
       </c>
       <c r="L236" s="2" t="n">
         <v>51.4</v>
       </c>
       <c r="M236" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N236" s="2" t="inlineStr"/>
       <c r="O236" s="2" t="inlineStr"/>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>Фишт</t>
+          <t>Розовая кора</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -16059,7 +15985,7 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>pal-051</t>
+          <t>pal-037</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -16074,22 +16000,22 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Черная Кора</t>
+          <t>Розовый Бриз</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>Коричневый</t>
+          <t>Розовый</t>
         </is>
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>коричневый</t>
+          <t>персиковый</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>руст</t>
+          <t>бриз</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -16098,23 +16024,25 @@
         </is>
       </c>
       <c r="I237" s="3" t="n">
-        <v>49.57</v>
+        <v>36.88</v>
       </c>
       <c r="J237" s="3" t="n"/>
       <c r="K237" s="2" t="inlineStr">
         <is>
-          <t>0,7НФ (евро): 45.50 ₽; 1,4НФ (полуторный): 62.83 ₽</t>
-        </is>
-      </c>
-      <c r="L237" s="2" t="n"/>
+          <t>0,7НФ (евро): 34.00 ₽; 1,4НФ (полуторный): 47.78 ₽</t>
+        </is>
+      </c>
+      <c r="L237" s="2" t="n">
+        <v>51.4</v>
+      </c>
       <c r="M237" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N237" s="2" t="inlineStr"/>
       <c r="O237" s="2" t="inlineStr"/>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>Черная кора</t>
+          <t>Розовый бриз</t>
         </is>
       </c>
       <c r="Q237" s="2" t="inlineStr">
@@ -16126,7 +16054,7 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>pal-052</t>
+          <t>pal-038</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -16141,17 +16069,17 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Черный Бриз</t>
+          <t>Розовый Мрамор</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>Коричневый</t>
+          <t>Бежевый</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>коричневый</t>
+          <t>серый</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
@@ -16165,23 +16093,29 @@
         </is>
       </c>
       <c r="I238" s="3" t="n">
-        <v>49.57</v>
+        <v>44.84</v>
       </c>
       <c r="J238" s="3" t="n"/>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>0,7НФ (евро): 45.50 ₽; 1,4НФ (полуторный): 62.83 ₽</t>
-        </is>
-      </c>
-      <c r="L238" s="2" t="n"/>
+          <t>0,9НФ: 44.84 ₽; 1,4НФ (полуторный): 55.04 ₽</t>
+        </is>
+      </c>
+      <c r="L238" s="2" t="n">
+        <v>51.4</v>
+      </c>
       <c r="M238" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N238" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="N238" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="O238" s="2" t="inlineStr"/>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>Черный бриз</t>
+          <t>Розовый мрамор</t>
         </is>
       </c>
       <c r="Q238" s="2" t="inlineStr">
@@ -16193,7 +16127,7 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>pal-053</t>
+          <t>pal-039</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
@@ -16208,17 +16142,17 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Эльбрус</t>
+          <t>СС-УС-01</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>Бежевый</t>
+          <t>Коричневый</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>бежевый</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
@@ -16231,30 +16165,24 @@
           <t>1НФ (одинарный)</t>
         </is>
       </c>
-      <c r="I239" s="3" t="n">
-        <v>44.84</v>
-      </c>
+      <c r="I239" s="3" t="n"/>
       <c r="J239" s="3" t="n"/>
-      <c r="K239" s="2" t="inlineStr">
-        <is>
-          <t>1,4НФ (полуторный): 55.04 ₽</t>
-        </is>
-      </c>
+      <c r="K239" s="2" t="inlineStr"/>
       <c r="L239" s="2" t="n">
         <v>51.4</v>
       </c>
-      <c r="M239" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N239" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="O239" s="2" t="inlineStr"/>
+      <c r="M239" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N239" s="2" t="inlineStr"/>
+      <c r="O239" s="4" t="inlineStr">
+        <is>
+          <t>нет фото</t>
+        </is>
+      </c>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>Эльбрус</t>
+          <t>01 СС УС</t>
         </is>
       </c>
       <c r="Q239" s="2" t="inlineStr">
@@ -16266,7 +16194,7 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>pal-054</t>
+          <t>pal-040</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -16281,17 +16209,17 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Янтарь</t>
+          <t>СС-УС-02</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>Розовый</t>
+          <t>Серый</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>бежевый</t>
+          <t>серый</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
@@ -16304,30 +16232,24 @@
           <t>1НФ (одинарный)</t>
         </is>
       </c>
-      <c r="I240" s="3" t="n">
-        <v>46.87</v>
-      </c>
+      <c r="I240" s="3" t="n"/>
       <c r="J240" s="3" t="n"/>
-      <c r="K240" s="2" t="inlineStr">
-        <is>
-          <t>1,4НФ (полуторный): 58.82 ₽</t>
-        </is>
-      </c>
+      <c r="K240" s="2" t="inlineStr"/>
       <c r="L240" s="2" t="n">
         <v>51.4</v>
       </c>
-      <c r="M240" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N240" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="O240" s="2" t="inlineStr"/>
+      <c r="M240" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N240" s="2" t="inlineStr"/>
+      <c r="O240" s="4" t="inlineStr">
+        <is>
+          <t>нет фото</t>
+        </is>
+      </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>Янтарь</t>
+          <t>02 СС УС</t>
         </is>
       </c>
       <c r="Q240" s="2" t="inlineStr">
@@ -16339,32 +16261,32 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>rab-003</t>
+          <t>pal-041</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Палитра</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Забутовочный</t>
+          <t>Облицовочный</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>КАМЕНЬ M175 (F75)</t>
+          <t>СС-УС-03.2</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>Розовый</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>персиковый</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
@@ -16377,57 +16299,61 @@
           <t>1НФ (одинарный)</t>
         </is>
       </c>
-      <c r="I241" s="3" t="n">
-        <v>38.5</v>
-      </c>
+      <c r="I241" s="3" t="n"/>
       <c r="J241" s="3" t="n"/>
       <c r="K241" s="2" t="inlineStr"/>
-      <c r="L241" s="2" t="n"/>
-      <c r="M241" s="2" t="n">
-        <v>3</v>
+      <c r="L241" s="2" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="M241" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="N241" s="2" t="inlineStr"/>
-      <c r="O241" s="2" t="inlineStr"/>
+      <c r="O241" s="4" t="inlineStr">
+        <is>
+          <t>нет фото</t>
+        </is>
+      </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>КАМЕНЬ M175 (F75) 192шт упак. пленкой</t>
+          <t>03.2 СС УС</t>
         </is>
       </c>
       <c r="Q241" s="2" t="inlineStr">
         <is>
-          <t>Донской</t>
+          <t>Губский</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>rab-004</t>
+          <t>pal-042</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Палитра</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Забутовочный</t>
+          <t>Облицовочный</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>КРАСНЫЙ Одинарный некондиционный</t>
+          <t>СС-УС-04</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>Желтый</t>
         </is>
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>бежевый</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
@@ -16440,61 +16366,61 @@
           <t>1НФ (одинарный)</t>
         </is>
       </c>
-      <c r="I242" s="3" t="n">
-        <v>11</v>
-      </c>
+      <c r="I242" s="3" t="n"/>
       <c r="J242" s="3" t="n"/>
       <c r="K242" s="2" t="inlineStr"/>
-      <c r="L242" s="2" t="n"/>
+      <c r="L242" s="2" t="n">
+        <v>51.4</v>
+      </c>
       <c r="M242" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N242" s="2" t="inlineStr"/>
       <c r="O242" s="4" t="inlineStr">
         <is>
-          <t>некондиция (уценка); нет фото</t>
+          <t>нет фото</t>
         </is>
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>КРАСНЫЙ Одинарный некондиционный 416шт упак. лентой</t>
+          <t>04 СС УС</t>
         </is>
       </c>
       <c r="Q242" s="2" t="inlineStr">
         <is>
-          <t>Донской</t>
+          <t>Губский</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>rab-005</t>
+          <t>pal-043</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Палитра</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>Забутовочный</t>
+          <t>Облицовочный</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Красный Одинарный М125 (F50)</t>
+          <t>СС-УС-05</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>Коричневый</t>
         </is>
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
@@ -16507,12 +16433,12 @@
           <t>1НФ (одинарный)</t>
         </is>
       </c>
-      <c r="I243" s="3" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="I243" s="3" t="n"/>
       <c r="J243" s="3" t="n"/>
       <c r="K243" s="2" t="inlineStr"/>
-      <c r="L243" s="2" t="n"/>
+      <c r="L243" s="2" t="n">
+        <v>51.4</v>
+      </c>
       <c r="M243" s="5" t="n">
         <v>0</v>
       </c>
@@ -16524,44 +16450,44 @@
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>Красный Одинарный М125 (F50) 416шт упак. пленкой и лентой</t>
+          <t>05 СС УС</t>
         </is>
       </c>
       <c r="Q243" s="2" t="inlineStr">
         <is>
-          <t>Донской</t>
+          <t>Губский</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>rab-006</t>
+          <t>pal-044</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Палитра</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Забутовочный</t>
+          <t>Облицовочный</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Одинарный М100 (F25 пустот. 12%, 8 конусных углублений)</t>
+          <t>СС-УС-06</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>Розовый</t>
         </is>
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>персиковый</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
@@ -16574,57 +16500,61 @@
           <t>1НФ (одинарный)</t>
         </is>
       </c>
-      <c r="I244" s="3" t="n">
-        <v>15</v>
-      </c>
+      <c r="I244" s="3" t="n"/>
       <c r="J244" s="3" t="n"/>
       <c r="K244" s="2" t="inlineStr"/>
-      <c r="L244" s="2" t="n"/>
-      <c r="M244" s="2" t="n">
-        <v>2</v>
+      <c r="L244" s="2" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="M244" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="N244" s="2" t="inlineStr"/>
-      <c r="O244" s="2" t="inlineStr"/>
+      <c r="O244" s="4" t="inlineStr">
+        <is>
+          <t>нет фото</t>
+        </is>
+      </c>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>Одинарный М100 (F25 пустот. 12%, 8 конусных углублений) 448шт</t>
+          <t>06 СС УС</t>
         </is>
       </c>
       <c r="Q244" s="2" t="inlineStr">
         <is>
-          <t>Донской</t>
+          <t>Губский</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>rab-007</t>
+          <t>pal-045</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Палитра</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>Забутовочный</t>
+          <t>Облицовочный</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Одинарный М100 (F25 пустот. 13%, 11 сквозных отверстий)</t>
+          <t>Сафари</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>Бежевый</t>
         </is>
       </c>
       <c r="F245" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>бежевый</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
@@ -16638,61 +16568,71 @@
         </is>
       </c>
       <c r="I245" s="3" t="n">
-        <v>15</v>
+        <v>45.86</v>
       </c>
       <c r="J245" s="3" t="n"/>
-      <c r="K245" s="2" t="inlineStr"/>
-      <c r="L245" s="2" t="n"/>
+      <c r="K245" s="2" t="inlineStr">
+        <is>
+          <t>0,7НФ (евро): 42.50 ₽; 1,4НФ (полуторный): 56.77 ₽</t>
+        </is>
+      </c>
+      <c r="L245" s="2" t="n">
+        <v>51.4</v>
+      </c>
       <c r="M245" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N245" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="N245" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="O245" s="2" t="inlineStr"/>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>Одинарный М100 (F25 пустот. 13%, 11 сквозных отверстий) 448шт</t>
+          <t>Сафари</t>
         </is>
       </c>
       <c r="Q245" s="2" t="inlineStr">
         <is>
-          <t>Донской</t>
+          <t>Губский</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>rab-008</t>
+          <t>pal-046</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Палитра</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Забутовочный</t>
+          <t>Облицовочный</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Одинарный М150 (F25 пустот. 12%, 8 конусных углублений)</t>
+          <t>Сахара</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>Красный</t>
         </is>
       </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>бежевый</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>гладкий</t>
+          <t>руст</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
@@ -16701,56 +16641,66 @@
         </is>
       </c>
       <c r="I246" s="3" t="n">
-        <v>15.35</v>
+        <v>25.64</v>
       </c>
       <c r="J246" s="3" t="n"/>
-      <c r="K246" s="2" t="inlineStr"/>
-      <c r="L246" s="2" t="n"/>
+      <c r="K246" s="2" t="inlineStr">
+        <is>
+          <t>1,4НФ (полуторный): 33.29 ₽</t>
+        </is>
+      </c>
+      <c r="L246" s="2" t="n">
+        <v>51.4</v>
+      </c>
       <c r="M246" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N246" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="N246" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="O246" s="2" t="inlineStr"/>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>Одинарный М150 (F25 пустот. 12%, 8 конусных углублений) 448шт</t>
+          <t>Сахара</t>
         </is>
       </c>
       <c r="Q246" s="2" t="inlineStr">
         <is>
-          <t>Донской</t>
+          <t>Губский</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>rab-009</t>
+          <t>pal-047</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Палитра</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>Забутовочный</t>
+          <t>Облицовочный</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>Одинарный М150 (F25 пустот. 13%, 11 сквозных отверстий)</t>
+          <t>Светло-бежевый</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>Бежевый</t>
         </is>
       </c>
       <c r="F247" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>бежевый</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
@@ -16764,58 +16714,68 @@
         </is>
       </c>
       <c r="I247" s="3" t="n">
-        <v>15.35</v>
+        <v>41.74</v>
       </c>
       <c r="J247" s="3" t="n"/>
-      <c r="K247" s="2" t="inlineStr"/>
-      <c r="L247" s="2" t="n"/>
+      <c r="K247" s="2" t="inlineStr">
+        <is>
+          <t>0,7НФ (евро): 38.55 ₽; 0,9НФ: 41.74 ₽; 1,4НФ (полуторный): 50.92 ₽</t>
+        </is>
+      </c>
+      <c r="L247" s="2" t="n">
+        <v>51.4</v>
+      </c>
       <c r="M247" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N247" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N247" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="O247" s="2" t="inlineStr"/>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>Одинарный М150 (F25 пустот. 13%, 11 сквозных отверстий) 448шт</t>
+          <t>Светло-бежевый</t>
         </is>
       </c>
       <c r="Q247" s="2" t="inlineStr">
         <is>
-          <t>Донской</t>
+          <t>Губский</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>rab-010</t>
+          <t>pal-048</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Палитра</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Забутовочный</t>
+          <t>Облицовочный</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>Одинарный полнотелый М150 (F25 пустот. 12%, 3 скв.отв)</t>
+          <t>Светло-гранатовый</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
+          <t>Бордовый</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
           <t>красный</t>
         </is>
       </c>
-      <c r="F248" s="2" t="inlineStr">
-        <is>
-          <t>красный</t>
-        </is>
-      </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
           <t>гладкий</t>
@@ -16827,56 +16787,66 @@
         </is>
       </c>
       <c r="I248" s="3" t="n">
-        <v>16.28</v>
+        <v>40.7</v>
       </c>
       <c r="J248" s="3" t="n"/>
-      <c r="K248" s="2" t="inlineStr"/>
-      <c r="L248" s="2" t="n"/>
+      <c r="K248" s="2" t="inlineStr">
+        <is>
+          <t>1,4НФ (полуторный): 51.41 ₽</t>
+        </is>
+      </c>
+      <c r="L248" s="2" t="n">
+        <v>51.4</v>
+      </c>
       <c r="M248" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N248" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="N248" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="O248" s="2" t="inlineStr"/>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>Одинарный полнотелый М150 (F25 пустот. 12%, 3 скв.отв) 480шт упак. лентой</t>
+          <t>Светло-гранатовый</t>
         </is>
       </c>
       <c r="Q248" s="2" t="inlineStr">
         <is>
-          <t>Донской</t>
+          <t>Губский</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>rab-011</t>
+          <t>pal-049</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Палитра</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>Забутовочный</t>
+          <t>Облицовочный</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>Одинарный полнотелый М150 (F35 пустот. 12%, 3 скв.отв)</t>
+          <t>Светло-зеленый</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>Зеленый</t>
         </is>
       </c>
       <c r="F249" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>зелёный</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
@@ -16890,56 +16860,62 @@
         </is>
       </c>
       <c r="I249" s="3" t="n">
-        <v>17.47</v>
+        <v>81.56</v>
       </c>
       <c r="J249" s="3" t="n"/>
       <c r="K249" s="2" t="inlineStr"/>
-      <c r="L249" s="2" t="n"/>
+      <c r="L249" s="2" t="n">
+        <v>51.4</v>
+      </c>
       <c r="M249" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N249" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="N249" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="O249" s="2" t="inlineStr"/>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>Одинарный полнотелый М150 (F35 пустот. 12%, 3 скв.отв) 480шт упак. лентой</t>
+          <t>Светло-зеленый</t>
         </is>
       </c>
       <c r="Q249" s="2" t="inlineStr">
         <is>
-          <t>Донской</t>
+          <t>Губский</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>rab-012</t>
+          <t>pal-050</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Палитра</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Забутовочный</t>
+          <t>Облицовочный</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>Одинарный полнотелый СВАР / некондиция</t>
+          <t>Светло-серый</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>Серый</t>
         </is>
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>серый</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
@@ -16953,60 +16929,66 @@
         </is>
       </c>
       <c r="I250" s="3" t="n">
-        <v>14.5</v>
+        <v>56.57</v>
       </c>
       <c r="J250" s="3" t="n"/>
-      <c r="K250" s="2" t="inlineStr"/>
-      <c r="L250" s="2" t="n"/>
-      <c r="M250" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N250" s="2" t="inlineStr"/>
-      <c r="O250" s="4" t="inlineStr">
-        <is>
-          <t>некондиция (уценка); нет фото</t>
-        </is>
-      </c>
+      <c r="K250" s="2" t="inlineStr">
+        <is>
+          <t>1,4НФ (полуторный): 70.85 ₽</t>
+        </is>
+      </c>
+      <c r="L250" s="2" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="M250" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N250" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="O250" s="2" t="inlineStr"/>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>Одинарный полнотелый СВАР / некондиция</t>
+          <t>Светло-серый</t>
         </is>
       </c>
       <c r="Q250" s="2" t="inlineStr">
         <is>
-          <t>Донской</t>
+          <t>Губский</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>rab-013</t>
+          <t>pal-051</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Палитра</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>Забутовочный</t>
+          <t>Облицовочный</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>Одинарный полнотелый сплошной М100 (F25)</t>
+          <t>Сиена Луч 1024</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>Коричневый</t>
         </is>
       </c>
       <c r="F251" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
@@ -17020,58 +17002,66 @@
         </is>
       </c>
       <c r="I251" s="3" t="n">
-        <v>19.98</v>
+        <v>39.74</v>
       </c>
       <c r="J251" s="3" t="n"/>
-      <c r="K251" s="2" t="inlineStr"/>
+      <c r="K251" s="2" t="inlineStr">
+        <is>
+          <t>1,4НФ (полуторный): 48.92 ₽</t>
+        </is>
+      </c>
       <c r="L251" s="2" t="n"/>
       <c r="M251" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N251" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="N251" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="O251" s="2" t="inlineStr"/>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>Одинарный полнотелый сплошной М100 (F25) 420шт упак. лентой</t>
+          <t>Сиена луч 1024</t>
         </is>
       </c>
       <c r="Q251" s="2" t="inlineStr">
         <is>
-          <t>Донской</t>
+          <t>Губский</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>rab-014</t>
+          <t>pal-052</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Палитра</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Забутовочный</t>
+          <t>Облицовочный</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Одинарный полнотелый сплошной М150 (F25)</t>
+          <t>Старый Город Бромо Про 26</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
+          <t>Красный</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
           <t>красный</t>
         </is>
       </c>
-      <c r="F252" s="2" t="inlineStr">
-        <is>
-          <t>красный</t>
-        </is>
-      </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
           <t>гладкий</t>
@@ -17083,56 +17073,56 @@
         </is>
       </c>
       <c r="I252" s="3" t="n">
-        <v>21.76</v>
+        <v>28.5</v>
       </c>
       <c r="J252" s="3" t="n"/>
       <c r="K252" s="2" t="inlineStr"/>
       <c r="L252" s="2" t="n"/>
       <c r="M252" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N252" s="2" t="inlineStr"/>
       <c r="O252" s="2" t="inlineStr"/>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>Одинарный полнотелый сплошной М150 (F25) 420шт упак. лентой</t>
+          <t>Старый город Бромо про 26</t>
         </is>
       </c>
       <c r="Q252" s="2" t="inlineStr">
         <is>
-          <t>Донской</t>
+          <t>Губский</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>rab-015</t>
+          <t>pal-053</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Палитра</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>Забутовочный</t>
+          <t>Облицовочный</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Одинарный полнотелый сплошной М150 (F35)</t>
+          <t>Старый Город Грей-по Рф</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>Серый</t>
         </is>
       </c>
       <c r="F253" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>серый</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
@@ -17146,61 +17136,61 @@
         </is>
       </c>
       <c r="I253" s="3" t="n">
-        <v>22.1</v>
+        <v>61</v>
       </c>
       <c r="J253" s="3" t="n"/>
       <c r="K253" s="2" t="inlineStr"/>
       <c r="L253" s="2" t="n"/>
       <c r="M253" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N253" s="2" t="inlineStr"/>
       <c r="O253" s="2" t="inlineStr"/>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>Одинарный полнотелый сплошной М150 (F35) 420шт упак. лентой</t>
+          <t>Старый город грей-по рф</t>
         </is>
       </c>
       <c r="Q253" s="2" t="inlineStr">
         <is>
-          <t>Донской</t>
+          <t>Губский</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>rab-001</t>
+          <t>pal-054</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Палитра</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Забутовочный</t>
+          <t>Облицовочный</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Рядовой пустотелый</t>
+          <t>Старый Город Графит</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>не регламентируется</t>
+          <t>Коричневый</t>
         </is>
       </c>
       <c r="F254" s="2" t="inlineStr">
         <is>
-          <t>разное</t>
+          <t>коричневый</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>гладкий</t>
+          <t>старый город</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
@@ -17209,23 +17199,23 @@
         </is>
       </c>
       <c r="I254" s="3" t="n">
-        <v>12</v>
+        <v>55.04</v>
       </c>
       <c r="J254" s="3" t="n"/>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>1НФ (одинарный): 12.00 ₽; 1,4НФ (полуторный): 15.50 ₽</t>
+          <t>1,4НФ (полуторный): 67.79 ₽</t>
         </is>
       </c>
       <c r="L254" s="2" t="n"/>
       <c r="M254" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N254" s="2" t="inlineStr"/>
       <c r="O254" s="2" t="inlineStr"/>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>Кирпич рядовой керамический пустотелый</t>
+          <t>Старый город графит</t>
         </is>
       </c>
       <c r="Q254" s="2" t="inlineStr">
@@ -17237,163 +17227,173 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>rab-016</t>
+          <t>pal-055</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Палитра</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>Забутовочный</t>
+          <t>Облицовочный</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>Утолщенный полнотелый М150 (F25 пустот. 12%, 3 скв.отв)</t>
+          <t>Старый Город Грей</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>Серый</t>
         </is>
       </c>
       <c r="F255" s="2" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>серый</t>
         </is>
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>гладкий</t>
+          <t>старый город</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>1,4НФ (полуторный)</t>
+          <t>1НФ (одинарный)</t>
         </is>
       </c>
       <c r="I255" s="3" t="n">
-        <v>25.5</v>
+        <v>58.1</v>
       </c>
       <c r="J255" s="3" t="n"/>
-      <c r="K255" s="2" t="inlineStr"/>
+      <c r="K255" s="2" t="inlineStr">
+        <is>
+          <t>1,4НФ (полуторный): 71.36 ₽</t>
+        </is>
+      </c>
       <c r="L255" s="2" t="n"/>
       <c r="M255" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N255" s="2" t="inlineStr"/>
       <c r="O255" s="2" t="inlineStr"/>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>Утолщенный полнотелый М150 (F25 пустот. 12%, 3 скв.отв) 352шт упак. лентой</t>
+          <t>Старый город грей</t>
         </is>
       </c>
       <c r="Q255" s="2" t="inlineStr">
         <is>
-          <t>Донской</t>
+          <t>Губский</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>rab-017</t>
+          <t>pal-056</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Палитра</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Забутовочный</t>
+          <t>Облицовочный</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Утолщенный полнотелый М150 сплошной (F25)</t>
+          <t>Старый Город Терра</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
+          <t>Красный</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
           <t>красный</t>
         </is>
       </c>
-      <c r="F256" s="2" t="inlineStr">
-        <is>
-          <t>красный</t>
-        </is>
-      </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>гладкий</t>
+          <t>старый город</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>1,4НФ (полуторный)</t>
+          <t>1НФ (одинарный)</t>
         </is>
       </c>
       <c r="I256" s="3" t="n">
-        <v>28.56</v>
+        <v>29.54</v>
       </c>
       <c r="J256" s="3" t="n"/>
-      <c r="K256" s="2" t="inlineStr"/>
-      <c r="L256" s="2" t="n"/>
+      <c r="K256" s="2" t="inlineStr">
+        <is>
+          <t>1,4НФ (полуторный): 36.17 ₽</t>
+        </is>
+      </c>
+      <c r="L256" s="2" t="n">
+        <v>51.4</v>
+      </c>
       <c r="M256" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N256" s="2" t="inlineStr"/>
       <c r="O256" s="2" t="inlineStr"/>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>Утолщенный полнотелый М150 сплошной (F25) 308шт упак. лентой</t>
+          <t>Старый город Терра</t>
         </is>
       </c>
       <c r="Q256" s="2" t="inlineStr">
         <is>
-          <t>Донской</t>
+          <t>Губский</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>rab-002</t>
+          <t>pal-057</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Палитра</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>Забутовочный</t>
+          <t>Облицовочный</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Хозяйственный пустотелый</t>
+          <t>Старый Город Терра Про</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>не регламентируется</t>
+          <t>Красный</t>
         </is>
       </c>
       <c r="F257" s="2" t="inlineStr">
         <is>
-          <t>разное</t>
+          <t>красный</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>гладкий</t>
+          <t>старый город</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -17402,33 +17402,1861 @@
         </is>
       </c>
       <c r="I257" s="3" t="n">
-        <v>8</v>
+        <v>31.58</v>
       </c>
       <c r="J257" s="3" t="n"/>
       <c r="K257" s="2" t="inlineStr">
         <is>
-          <t>1НФ (одинарный): 8.00 ₽; 1,4НФ (полуторный): 11.00 ₽</t>
-        </is>
-      </c>
-      <c r="L257" s="2" t="n"/>
+          <t>1,4НФ (полуторный): 38.72 ₽</t>
+        </is>
+      </c>
+      <c r="L257" s="2" t="n">
+        <v>51.4</v>
+      </c>
       <c r="M257" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N257" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="N257" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="O257" s="2" t="inlineStr"/>
       <c r="P257" s="2" t="inlineStr">
         <is>
+          <t>Старый город Терра Про</t>
+        </is>
+      </c>
+      <c r="Q257" s="2" t="inlineStr">
+        <is>
+          <t>Губский</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>pal-058</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>Палитра</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>Облицовочный</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>Старый Город Терра Про-по Рф</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>Красный</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>старый город</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I258" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="J258" s="3" t="n"/>
+      <c r="K258" s="2" t="inlineStr"/>
+      <c r="L258" s="2" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="M258" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N258" s="2" t="inlineStr"/>
+      <c r="O258" s="2" t="inlineStr"/>
+      <c r="P258" s="2" t="inlineStr">
+        <is>
+          <t>Старый Город Терра Про-по рф</t>
+        </is>
+      </c>
+      <c r="Q258" s="2" t="inlineStr">
+        <is>
+          <t>Губский</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>pal-059</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>Палитра</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>Облицовочный</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>Старый Город Терра-по Рф</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>Красный</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>старый город</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I259" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="J259" s="3" t="n"/>
+      <c r="K259" s="2" t="inlineStr"/>
+      <c r="L259" s="2" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="M259" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N259" s="2" t="inlineStr"/>
+      <c r="O259" s="2" t="inlineStr"/>
+      <c r="P259" s="2" t="inlineStr">
+        <is>
+          <t>Старый Город Терра-по рф</t>
+        </is>
+      </c>
+      <c r="Q259" s="2" t="inlineStr">
+        <is>
+          <t>Губский</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>pal-060</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>Палитра</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>Облицовочный</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>УС-01.04</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>Коричневый</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>коричневый</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>гладкий</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I260" s="3" t="n"/>
+      <c r="J260" s="3" t="n"/>
+      <c r="K260" s="2" t="inlineStr"/>
+      <c r="L260" s="2" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="M260" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N260" s="2" t="inlineStr"/>
+      <c r="O260" s="2" t="inlineStr"/>
+      <c r="P260" s="2" t="inlineStr">
+        <is>
+          <t>01.04.2026 УС</t>
+        </is>
+      </c>
+      <c r="Q260" s="2" t="inlineStr">
+        <is>
+          <t>Губский</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>pal-061</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>Палитра</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>Облицовочный</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>Фишт</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>Бежевый</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>бежевый</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>гладкий</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I261" s="3" t="n">
+        <v>44.84</v>
+      </c>
+      <c r="J261" s="3" t="n"/>
+      <c r="K261" s="2" t="inlineStr">
+        <is>
+          <t>1,4НФ (полуторный): 55.04 ₽</t>
+        </is>
+      </c>
+      <c r="L261" s="2" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="M261" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N261" s="2" t="inlineStr"/>
+      <c r="O261" s="2" t="inlineStr"/>
+      <c r="P261" s="2" t="inlineStr">
+        <is>
+          <t>Фишт</t>
+        </is>
+      </c>
+      <c r="Q261" s="2" t="inlineStr">
+        <is>
+          <t>Губский</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>pal-062</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>Палитра</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>Облицовочный</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>Черная Кора</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>Коричневый</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>коричневый</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>руст</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I262" s="3" t="n">
+        <v>49.57</v>
+      </c>
+      <c r="J262" s="3" t="n"/>
+      <c r="K262" s="2" t="inlineStr">
+        <is>
+          <t>0,7НФ (евро): 45.50 ₽; 1,4НФ (полуторный): 62.83 ₽</t>
+        </is>
+      </c>
+      <c r="L262" s="2" t="n"/>
+      <c r="M262" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N262" s="2" t="inlineStr"/>
+      <c r="O262" s="2" t="inlineStr"/>
+      <c r="P262" s="2" t="inlineStr">
+        <is>
+          <t>Черная кора</t>
+        </is>
+      </c>
+      <c r="Q262" s="2" t="inlineStr">
+        <is>
+          <t>Губский</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>pal-063</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>Палитра</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>Облицовочный</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>Черный Бриз</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>Коричневый</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>коричневый</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>руст</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I263" s="3" t="n">
+        <v>49.57</v>
+      </c>
+      <c r="J263" s="3" t="n"/>
+      <c r="K263" s="2" t="inlineStr">
+        <is>
+          <t>0,7НФ (евро): 45.50 ₽; 1,4НФ (полуторный): 62.83 ₽</t>
+        </is>
+      </c>
+      <c r="L263" s="2" t="n"/>
+      <c r="M263" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N263" s="2" t="inlineStr"/>
+      <c r="O263" s="2" t="inlineStr"/>
+      <c r="P263" s="2" t="inlineStr">
+        <is>
+          <t>Черный бриз</t>
+        </is>
+      </c>
+      <c r="Q263" s="2" t="inlineStr">
+        <is>
+          <t>Губский</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>pal-064</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>Палитра</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>Облицовочный</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>Эльбрус</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>Бежевый</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>бежевый</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>гладкий</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I264" s="3" t="n">
+        <v>44.84</v>
+      </c>
+      <c r="J264" s="3" t="n"/>
+      <c r="K264" s="2" t="inlineStr">
+        <is>
+          <t>1,4НФ (полуторный): 55.04 ₽</t>
+        </is>
+      </c>
+      <c r="L264" s="2" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="M264" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N264" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="O264" s="2" t="inlineStr"/>
+      <c r="P264" s="2" t="inlineStr">
+        <is>
+          <t>Эльбрус</t>
+        </is>
+      </c>
+      <c r="Q264" s="2" t="inlineStr">
+        <is>
+          <t>Губский</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>pal-065</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>Палитра</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>Облицовочный</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>Янтарь</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>Розовый</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>бежевый</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>гладкий</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I265" s="3" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="J265" s="3" t="n"/>
+      <c r="K265" s="2" t="inlineStr">
+        <is>
+          <t>1,4НФ (полуторный): 58.82 ₽</t>
+        </is>
+      </c>
+      <c r="L265" s="2" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="M265" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N265" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="O265" s="2" t="inlineStr"/>
+      <c r="P265" s="2" t="inlineStr">
+        <is>
+          <t>Янтарь</t>
+        </is>
+      </c>
+      <c r="Q265" s="2" t="inlineStr">
+        <is>
+          <t>Губский</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>rab-003</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>Забутовочный</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>БАВАРСКИЙ СВЕТЛЫЙ ВЕЛЬВЕТ Рядовой Одинарный М175 (F75)</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>микс (бавария)</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>микс (бавария)</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>велюр</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I266" s="3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="J266" s="3" t="n"/>
+      <c r="K266" s="2" t="inlineStr"/>
+      <c r="L266" s="2" t="n"/>
+      <c r="M266" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N266" s="2" t="inlineStr"/>
+      <c r="O266" s="2" t="inlineStr"/>
+      <c r="P266" s="2" t="inlineStr">
+        <is>
+          <t>БАВАРСКИЙ СВЕТЛЫЙ ВЕЛЬВЕТ Рядовой Одинарный М175 (F75) 416шт упак. пленкой</t>
+        </is>
+      </c>
+      <c r="Q266" s="2" t="inlineStr">
+        <is>
+          <t>Донской</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>rab-004</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>Забутовочный</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>БЕЛЫЕ НОЧИ БЕРЕСТА Рядовой Одинарный М150 (F50)</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>белый</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>белый</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>береста</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I267" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="J267" s="3" t="n"/>
+      <c r="K267" s="2" t="inlineStr"/>
+      <c r="L267" s="2" t="n"/>
+      <c r="M267" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N267" s="2" t="inlineStr"/>
+      <c r="O267" s="2" t="inlineStr"/>
+      <c r="P267" s="2" t="inlineStr">
+        <is>
+          <t>БЕЛЫЕ НОЧИ БЕРЕСТА Рядовой Одинарный М150 (F50) 416шт упак. пленкой</t>
+        </is>
+      </c>
+      <c r="Q267" s="2" t="inlineStr">
+        <is>
+          <t>Донской</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>rab-005</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>Забутовочный</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>БЕЛЫЕ НОЧИ Рядовой Одинарный М150 (F50)</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>белый</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>белый</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>гладкий</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I268" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="J268" s="3" t="n"/>
+      <c r="K268" s="2" t="inlineStr"/>
+      <c r="L268" s="2" t="n"/>
+      <c r="M268" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N268" s="2" t="inlineStr"/>
+      <c r="O268" s="2" t="inlineStr"/>
+      <c r="P268" s="2" t="inlineStr">
+        <is>
+          <t>БЕЛЫЕ НОЧИ Рядовой Одинарный М150 (F50) 416шт упак. пленкой</t>
+        </is>
+      </c>
+      <c r="Q268" s="2" t="inlineStr">
+        <is>
+          <t>Донской</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>rab-006</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>Забутовочный</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>КАМЕНЬ M175 (F75)</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>гладкий</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I269" s="3" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="J269" s="3" t="n"/>
+      <c r="K269" s="2" t="inlineStr"/>
+      <c r="L269" s="2" t="n"/>
+      <c r="M269" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N269" s="2" t="inlineStr"/>
+      <c r="O269" s="2" t="inlineStr"/>
+      <c r="P269" s="2" t="inlineStr">
+        <is>
+          <t>КАМЕНЬ M175 (F75) 192шт упак. пленкой</t>
+        </is>
+      </c>
+      <c r="Q269" s="2" t="inlineStr">
+        <is>
+          <t>Донской</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>rab-007</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>Забутовочный</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>КРАСНЫЙ Одинарный некондиционный</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>гладкий</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I270" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="J270" s="3" t="n"/>
+      <c r="K270" s="2" t="inlineStr"/>
+      <c r="L270" s="2" t="n"/>
+      <c r="M270" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N270" s="2" t="inlineStr"/>
+      <c r="O270" s="4" t="inlineStr">
+        <is>
+          <t>некондиция (уценка); нет фото</t>
+        </is>
+      </c>
+      <c r="P270" s="2" t="inlineStr">
+        <is>
+          <t>КРАСНЫЙ Одинарный некондиционный 416шт упак. лентой</t>
+        </is>
+      </c>
+      <c r="Q270" s="2" t="inlineStr">
+        <is>
+          <t>Донской</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>rab-008</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>Забутовочный</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>Красный Одинарный М125 (F50)</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>гладкий</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I271" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="J271" s="3" t="n"/>
+      <c r="K271" s="2" t="inlineStr"/>
+      <c r="L271" s="2" t="n"/>
+      <c r="M271" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N271" s="2" t="inlineStr"/>
+      <c r="O271" s="4" t="inlineStr">
+        <is>
+          <t>нет фото</t>
+        </is>
+      </c>
+      <c r="P271" s="2" t="inlineStr">
+        <is>
+          <t>Красный Одинарный М125 (F50) 416шт упак. пленкой и лентой</t>
+        </is>
+      </c>
+      <c r="Q271" s="2" t="inlineStr">
+        <is>
+          <t>Донской</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>rab-009</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>Забутовочный</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>Одинарный М100 (F25 пустот. 12%, 8 конусных углублений)</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>гладкий</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I272" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J272" s="3" t="n"/>
+      <c r="K272" s="2" t="inlineStr"/>
+      <c r="L272" s="2" t="n"/>
+      <c r="M272" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N272" s="2" t="inlineStr"/>
+      <c r="O272" s="2" t="inlineStr"/>
+      <c r="P272" s="2" t="inlineStr">
+        <is>
+          <t>Одинарный М100 (F25 пустот. 12%, 8 конусных углублений) 448шт</t>
+        </is>
+      </c>
+      <c r="Q272" s="2" t="inlineStr">
+        <is>
+          <t>Донской</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>rab-010</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>Забутовочный</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>Одинарный М100 (F25 пустот. 13%, 11 сквозных отверстий)</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>гладкий</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I273" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J273" s="3" t="n"/>
+      <c r="K273" s="2" t="inlineStr"/>
+      <c r="L273" s="2" t="n"/>
+      <c r="M273" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N273" s="2" t="inlineStr"/>
+      <c r="O273" s="2" t="inlineStr"/>
+      <c r="P273" s="2" t="inlineStr">
+        <is>
+          <t>Одинарный М100 (F25 пустот. 13%, 11 сквозных отверстий) 448шт</t>
+        </is>
+      </c>
+      <c r="Q273" s="2" t="inlineStr">
+        <is>
+          <t>Донской</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>rab-011</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>Забутовочный</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>Одинарный М150 (F25 пустот. 12%, 8 конусных углублений)</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>гладкий</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I274" s="3" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="J274" s="3" t="n"/>
+      <c r="K274" s="2" t="inlineStr"/>
+      <c r="L274" s="2" t="n"/>
+      <c r="M274" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N274" s="2" t="inlineStr"/>
+      <c r="O274" s="2" t="inlineStr"/>
+      <c r="P274" s="2" t="inlineStr">
+        <is>
+          <t>Одинарный М150 (F25 пустот. 12%, 8 конусных углублений) 448шт</t>
+        </is>
+      </c>
+      <c r="Q274" s="2" t="inlineStr">
+        <is>
+          <t>Донской</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>rab-012</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>Забутовочный</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>Одинарный М150 (F25 пустот. 13%, 11 сквозных отверстий)</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>гладкий</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I275" s="3" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="J275" s="3" t="n"/>
+      <c r="K275" s="2" t="inlineStr"/>
+      <c r="L275" s="2" t="n"/>
+      <c r="M275" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N275" s="2" t="inlineStr"/>
+      <c r="O275" s="2" t="inlineStr"/>
+      <c r="P275" s="2" t="inlineStr">
+        <is>
+          <t>Одинарный М150 (F25 пустот. 13%, 11 сквозных отверстий) 448шт</t>
+        </is>
+      </c>
+      <c r="Q275" s="2" t="inlineStr">
+        <is>
+          <t>Донской</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>rab-013</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>Забутовочный</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>Одинарный полнотелый М150 (F25 пустот. 12%, 3 скв.отв)</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>гладкий</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I276" s="3" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="J276" s="3" t="n"/>
+      <c r="K276" s="2" t="inlineStr"/>
+      <c r="L276" s="2" t="n"/>
+      <c r="M276" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N276" s="2" t="inlineStr"/>
+      <c r="O276" s="2" t="inlineStr"/>
+      <c r="P276" s="2" t="inlineStr">
+        <is>
+          <t>Одинарный полнотелый М150 (F25 пустот. 12%, 3 скв.отв) 480шт упак. лентой</t>
+        </is>
+      </c>
+      <c r="Q276" s="2" t="inlineStr">
+        <is>
+          <t>Донской</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>rab-014</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>Забутовочный</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>Одинарный полнотелый М150 (F35 пустот. 12%, 3 скв.отв)</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>гладкий</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I277" s="3" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="J277" s="3" t="n"/>
+      <c r="K277" s="2" t="inlineStr"/>
+      <c r="L277" s="2" t="n"/>
+      <c r="M277" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N277" s="2" t="inlineStr"/>
+      <c r="O277" s="2" t="inlineStr"/>
+      <c r="P277" s="2" t="inlineStr">
+        <is>
+          <t>Одинарный полнотелый М150 (F35 пустот. 12%, 3 скв.отв) 480шт упак. лентой</t>
+        </is>
+      </c>
+      <c r="Q277" s="2" t="inlineStr">
+        <is>
+          <t>Донской</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>rab-015</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>Забутовочный</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>Одинарный полнотелый СВАР / некондиция</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>гладкий</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I278" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="J278" s="3" t="n"/>
+      <c r="K278" s="2" t="inlineStr"/>
+      <c r="L278" s="2" t="n"/>
+      <c r="M278" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N278" s="2" t="inlineStr"/>
+      <c r="O278" s="4" t="inlineStr">
+        <is>
+          <t>некондиция (уценка); нет фото</t>
+        </is>
+      </c>
+      <c r="P278" s="2" t="inlineStr">
+        <is>
+          <t>Одинарный полнотелый СВАР / некондиция</t>
+        </is>
+      </c>
+      <c r="Q278" s="2" t="inlineStr">
+        <is>
+          <t>Донской</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>rab-016</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>Забутовочный</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>Одинарный полнотелый сплошной М100 (F25)</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>гладкий</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I279" s="3" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="J279" s="3" t="n"/>
+      <c r="K279" s="2" t="inlineStr"/>
+      <c r="L279" s="2" t="n"/>
+      <c r="M279" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N279" s="2" t="inlineStr"/>
+      <c r="O279" s="2" t="inlineStr"/>
+      <c r="P279" s="2" t="inlineStr">
+        <is>
+          <t>Одинарный полнотелый сплошной М100 (F25) 420шт упак. лентой</t>
+        </is>
+      </c>
+      <c r="Q279" s="2" t="inlineStr">
+        <is>
+          <t>Донской</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>rab-017</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>Забутовочный</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>Одинарный полнотелый сплошной М150 (F25)</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>гладкий</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I280" s="3" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="J280" s="3" t="n"/>
+      <c r="K280" s="2" t="inlineStr"/>
+      <c r="L280" s="2" t="n"/>
+      <c r="M280" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N280" s="2" t="inlineStr"/>
+      <c r="O280" s="2" t="inlineStr"/>
+      <c r="P280" s="2" t="inlineStr">
+        <is>
+          <t>Одинарный полнотелый сплошной М150 (F25) 420шт упак. лентой</t>
+        </is>
+      </c>
+      <c r="Q280" s="2" t="inlineStr">
+        <is>
+          <t>Донской</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>rab-018</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>Забутовочный</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>Одинарный полнотелый сплошной М150 (F35)</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>гладкий</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I281" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="J281" s="3" t="n"/>
+      <c r="K281" s="2" t="inlineStr"/>
+      <c r="L281" s="2" t="n"/>
+      <c r="M281" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N281" s="2" t="inlineStr"/>
+      <c r="O281" s="2" t="inlineStr"/>
+      <c r="P281" s="2" t="inlineStr">
+        <is>
+          <t>Одинарный полнотелый сплошной М150 (F35) 420шт упак. лентой</t>
+        </is>
+      </c>
+      <c r="Q281" s="2" t="inlineStr">
+        <is>
+          <t>Донской</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>rab-001</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>Забутовочный</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>Рядовой пустотелый</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>не регламентируется</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>разное</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>гладкий</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I282" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J282" s="3" t="n"/>
+      <c r="K282" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный): 12.00 ₽; 1,4НФ (полуторный): 15.50 ₽</t>
+        </is>
+      </c>
+      <c r="L282" s="2" t="n"/>
+      <c r="M282" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N282" s="2" t="inlineStr"/>
+      <c r="O282" s="2" t="inlineStr"/>
+      <c r="P282" s="2" t="inlineStr">
+        <is>
+          <t>Кирпич рядовой керамический пустотелый</t>
+        </is>
+      </c>
+      <c r="Q282" s="2" t="inlineStr">
+        <is>
+          <t>Губский</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>rab-019</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>Забутовочный</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>Утолщенный полнотелый М150 (F25 пустот. 12%, 3 скв.отв)</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>гладкий</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>1,4НФ (полуторный)</t>
+        </is>
+      </c>
+      <c r="I283" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="J283" s="3" t="n"/>
+      <c r="K283" s="2" t="inlineStr"/>
+      <c r="L283" s="2" t="n"/>
+      <c r="M283" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N283" s="2" t="inlineStr"/>
+      <c r="O283" s="2" t="inlineStr"/>
+      <c r="P283" s="2" t="inlineStr">
+        <is>
+          <t>Утолщенный полнотелый М150 (F25 пустот. 12%, 3 скв.отв) 352шт упак. лентой</t>
+        </is>
+      </c>
+      <c r="Q283" s="2" t="inlineStr">
+        <is>
+          <t>Донской</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>rab-020</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>Забутовочный</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>Утолщенный полнотелый М150 сплошной (F25)</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>красный</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>гладкий</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="inlineStr">
+        <is>
+          <t>1,4НФ (полуторный)</t>
+        </is>
+      </c>
+      <c r="I284" s="3" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="J284" s="3" t="n"/>
+      <c r="K284" s="2" t="inlineStr"/>
+      <c r="L284" s="2" t="n"/>
+      <c r="M284" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N284" s="2" t="inlineStr"/>
+      <c r="O284" s="2" t="inlineStr"/>
+      <c r="P284" s="2" t="inlineStr">
+        <is>
+          <t>Утолщенный полнотелый М150 сплошной (F25) 308шт упак. лентой</t>
+        </is>
+      </c>
+      <c r="Q284" s="2" t="inlineStr">
+        <is>
+          <t>Донской</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>rab-002</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>Забутовочный</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>Хозяйственный пустотелый</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>не регламентируется</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>разное</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>гладкий</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный)</t>
+        </is>
+      </c>
+      <c r="I285" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J285" s="3" t="n"/>
+      <c r="K285" s="2" t="inlineStr">
+        <is>
+          <t>1НФ (одинарный): 8.00 ₽; 1,4НФ (полуторный): 11.00 ₽</t>
+        </is>
+      </c>
+      <c r="L285" s="2" t="n"/>
+      <c r="M285" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N285" s="2" t="inlineStr"/>
+      <c r="O285" s="2" t="inlineStr"/>
+      <c r="P285" s="2" t="inlineStr">
+        <is>
           <t>Кирпич хозяйственный керамический пустотелый</t>
         </is>
       </c>
-      <c r="Q257" s="2" t="inlineStr">
+      <c r="Q285" s="2" t="inlineStr">
         <is>
           <t>Губский</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q257"/>
+  <autoFilter ref="A1:Q285"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17458,7 +19286,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Собрано автоматически из папки фото · 2026-07-16</t>
+          <t>Собрано автоматически из папки фото · 2026-07-17</t>
         </is>
       </c>
     </row>
@@ -17472,7 +19300,7 @@
         </is>
       </c>
       <c r="B4" s="9">
-        <f>COUNTA(Каталог!A2:A257)</f>
+        <f>COUNTA(Каталог!A2:A285)</f>
         <v/>
       </c>
     </row>
@@ -17483,7 +19311,7 @@
         </is>
       </c>
       <c r="B5" s="9">
-        <f>COUNTIF(Каталог!C2:C257,"Облицовочный")</f>
+        <f>COUNTIF(Каталог!C2:C285,"Облицовочный")</f>
         <v/>
       </c>
     </row>
@@ -17494,7 +19322,7 @@
         </is>
       </c>
       <c r="B6" s="9">
-        <f>COUNTIF(Каталог!C2:C257,"Забутовочный")</f>
+        <f>COUNTIF(Каталог!C2:C285,"Забутовочный")</f>
         <v/>
       </c>
     </row>
@@ -17505,7 +19333,7 @@
         </is>
       </c>
       <c r="B7" s="9">
-        <f>COUNTIF(Каталог!M2:M257,0)</f>
+        <f>COUNTIF(Каталог!M2:M285,0)</f>
         <v/>
       </c>
     </row>
@@ -17516,7 +19344,7 @@
         </is>
       </c>
       <c r="B8" s="9">
-        <f>COUNTBLANK(Каталог!I2:I257)</f>
+        <f>COUNTBLANK(Каталог!I2:I285)</f>
         <v/>
       </c>
     </row>
@@ -17527,7 +19355,7 @@
         </is>
       </c>
       <c r="B9" s="9">
-        <f>COUNTIF(Каталог!N2:N257,"да")</f>
+        <f>COUNTIF(Каталог!N2:N285,"да")</f>
         <v/>
       </c>
     </row>
@@ -17558,15 +19386,15 @@
         </is>
       </c>
       <c r="B12" s="9">
-        <f>COUNTIF(Каталог!B2:B257,"Эконом")</f>
+        <f>COUNTIF(Каталог!B2:B285,"Эконом")</f>
         <v/>
       </c>
       <c r="C12" s="11">
-        <f>MINIFS(Каталог!I2:I257,Каталог!B2:B257,"Эконом")</f>
+        <f>MINIFS(Каталог!I2:I285,Каталог!B2:B285,"Эконом")</f>
         <v/>
       </c>
       <c r="D12" s="11">
-        <f>MAXIFS(Каталог!I2:I257,Каталог!B2:B257,"Эконом")</f>
+        <f>MAXIFS(Каталог!I2:I285,Каталог!B2:B285,"Эконом")</f>
         <v/>
       </c>
     </row>
@@ -17577,15 +19405,15 @@
         </is>
       </c>
       <c r="B13" s="9">
-        <f>COUNTIF(Каталог!B2:B257,"Палитра")</f>
+        <f>COUNTIF(Каталог!B2:B285,"Палитра")</f>
         <v/>
       </c>
       <c r="C13" s="11">
-        <f>MINIFS(Каталог!I2:I257,Каталог!B2:B257,"Палитра")</f>
+        <f>MINIFS(Каталог!I2:I285,Каталог!B2:B285,"Палитра")</f>
         <v/>
       </c>
       <c r="D13" s="11">
-        <f>MAXIFS(Каталог!I2:I257,Каталог!B2:B257,"Палитра")</f>
+        <f>MAXIFS(Каталог!I2:I285,Каталог!B2:B285,"Палитра")</f>
         <v/>
       </c>
     </row>
@@ -17596,15 +19424,15 @@
         </is>
       </c>
       <c r="B14" s="9">
-        <f>COUNTIF(Каталог!B2:B257,"Классика")</f>
+        <f>COUNTIF(Каталог!B2:B285,"Классика")</f>
         <v/>
       </c>
       <c r="C14" s="11">
-        <f>MINIFS(Каталог!I2:I257,Каталог!B2:B257,"Классика")</f>
+        <f>MINIFS(Каталог!I2:I285,Каталог!B2:B285,"Классика")</f>
         <v/>
       </c>
       <c r="D14" s="11">
-        <f>MAXIFS(Каталог!I2:I257,Каталог!B2:B257,"Классика")</f>
+        <f>MAXIFS(Каталог!I2:I285,Каталог!B2:B285,"Классика")</f>
         <v/>
       </c>
     </row>
@@ -17615,15 +19443,15 @@
         </is>
       </c>
       <c r="B15" s="9">
-        <f>COUNTIF(Каталог!B2:B257,"Европа")</f>
+        <f>COUNTIF(Каталог!B2:B285,"Европа")</f>
         <v/>
       </c>
       <c r="C15" s="11">
-        <f>MINIFS(Каталог!I2:I257,Каталог!B2:B257,"Европа")</f>
+        <f>MINIFS(Каталог!I2:I285,Каталог!B2:B285,"Европа")</f>
         <v/>
       </c>
       <c r="D15" s="11">
-        <f>MAXIFS(Каталог!I2:I257,Каталог!B2:B257,"Европа")</f>
+        <f>MAXIFS(Каталог!I2:I285,Каталог!B2:B285,"Европа")</f>
         <v/>
       </c>
     </row>
@@ -17634,15 +19462,15 @@
         </is>
       </c>
       <c r="B16" s="9">
-        <f>COUNTIF(Каталог!B2:B257,"Ручная формовка")</f>
+        <f>COUNTIF(Каталог!B2:B285,"Ручная формовка")</f>
         <v/>
       </c>
       <c r="C16" s="11">
-        <f>MINIFS(Каталог!I2:I257,Каталог!B2:B257,"Ручная формовка")</f>
+        <f>MINIFS(Каталог!I2:I285,Каталог!B2:B285,"Ручная формовка")</f>
         <v/>
       </c>
       <c r="D16" s="11">
-        <f>MAXIFS(Каталог!I2:I257,Каталог!B2:B257,"Ручная формовка")</f>
+        <f>MAXIFS(Каталог!I2:I285,Каталог!B2:B285,"Ручная формовка")</f>
         <v/>
       </c>
     </row>
@@ -17660,7 +19488,7 @@
         </is>
       </c>
       <c r="B19" s="9">
-        <f>COUNTIFS(Каталог!F2:F257,"бежевый",Каталог!C2:C257,"Облицовочный")</f>
+        <f>COUNTIFS(Каталог!F2:F285,"бежевый",Каталог!C2:C285,"Облицовочный")</f>
         <v/>
       </c>
     </row>
@@ -17671,7 +19499,7 @@
         </is>
       </c>
       <c r="B20" s="9">
-        <f>COUNTIFS(Каталог!F2:F257,"графит",Каталог!C2:C257,"Облицовочный")</f>
+        <f>COUNTIFS(Каталог!F2:F285,"графит",Каталог!C2:C285,"Облицовочный")</f>
         <v/>
       </c>
     </row>
@@ -17682,7 +19510,7 @@
         </is>
       </c>
       <c r="B21" s="9">
-        <f>COUNTIFS(Каталог!F2:F257,"зелёный",Каталог!C2:C257,"Облицовочный")</f>
+        <f>COUNTIFS(Каталог!F2:F285,"зелёный",Каталог!C2:C285,"Облицовочный")</f>
         <v/>
       </c>
     </row>
@@ -17693,7 +19521,7 @@
         </is>
       </c>
       <c r="B22" s="9">
-        <f>COUNTIFS(Каталог!F2:F257,"коричневый",Каталог!C2:C257,"Облицовочный")</f>
+        <f>COUNTIFS(Каталог!F2:F285,"коричневый",Каталог!C2:C285,"Облицовочный")</f>
         <v/>
       </c>
     </row>
@@ -17704,7 +19532,7 @@
         </is>
       </c>
       <c r="B23" s="9">
-        <f>COUNTIFS(Каталог!F2:F257,"красный",Каталог!C2:C257,"Облицовочный")</f>
+        <f>COUNTIFS(Каталог!F2:F285,"красный",Каталог!C2:C285,"Облицовочный")</f>
         <v/>
       </c>
     </row>
@@ -17715,7 +19543,7 @@
         </is>
       </c>
       <c r="B24" s="9">
-        <f>COUNTIFS(Каталог!F2:F257,"микс (бавария)",Каталог!C2:C257,"Облицовочный")</f>
+        <f>COUNTIFS(Каталог!F2:F285,"микс (бавария)",Каталог!C2:C285,"Облицовочный")</f>
         <v/>
       </c>
     </row>
@@ -17726,7 +19554,7 @@
         </is>
       </c>
       <c r="B25" s="9">
-        <f>COUNTIFS(Каталог!F2:F257,"персиковый",Каталог!C2:C257,"Облицовочный")</f>
+        <f>COUNTIFS(Каталог!F2:F285,"персиковый",Каталог!C2:C285,"Облицовочный")</f>
         <v/>
       </c>
     </row>
@@ -17737,7 +19565,7 @@
         </is>
       </c>
       <c r="B26" s="9">
-        <f>COUNTIFS(Каталог!F2:F257,"разное",Каталог!C2:C257,"Облицовочный")</f>
+        <f>COUNTIFS(Каталог!F2:F285,"разное",Каталог!C2:C285,"Облицовочный")</f>
         <v/>
       </c>
     </row>
@@ -17748,7 +19576,7 @@
         </is>
       </c>
       <c r="B27" s="9">
-        <f>COUNTIFS(Каталог!F2:F257,"серый",Каталог!C2:C257,"Облицовочный")</f>
+        <f>COUNTIFS(Каталог!F2:F285,"серый",Каталог!C2:C285,"Облицовочный")</f>
         <v/>
       </c>
     </row>

--- a/КАТАЛОГ-ТАБЛИЦА.xlsx
+++ b/КАТАЛОГ-ТАБЛИЦА.xlsx
@@ -10,10 +10,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Каталог" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Плитка" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кровля" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Каталог'!$A$1:$Q$285</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Плитка'!$A$1:$J$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Кровля'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -28330,4 +28332,765 @@
   <autoFilter ref="A1:J175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Вид</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Название на сайте</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Коротко</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Цветов</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Фото</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Чертёж</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Цена</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Поставщик (на сайт НЕ выводим)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>krovlya-mch-monterrey</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Металлочерепица</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Супермонтеррей</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>классический профиль · волна 24 мм</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>EURO-Профиль</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>krovlya-mch-dyuna</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Металлочерепица</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Испанская дюна</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>модульный профиль · скрытое крепление</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>EURO-Профиль</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>krovlya-prof-s8</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Профнастил</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>С-8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>заборы и обшивка · волна 8 мм</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>EURO-Профиль</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>krovlya-prof-s10</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Профнастил</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>С-10</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>заборы и стены · волна 10 мм</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>EURO-Профиль</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>krovlya-prof-s21</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Профнастил</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>С-21</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>универсальный · волна 21 мм</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>EURO-Профиль</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>krovlya-prof-mp20</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Профнастил</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>МП-20</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>кровля и заборы · волна 20 мм</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>EURO-Профиль</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>krovlya-prof-ns35</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Профнастил</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>НС-35</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>кровля и навесы · волна 35 мм</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>EURO-Профиль</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>krovlya-prof-n60</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Профнастил</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Н-60</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>несущий · волна 60 мм</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>EURO-Профиль</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>krovlya-sht-kruglyy</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Штакетник</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Евроштакетник круглый</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>скруглённый верх · ширина 130 мм</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>EURO-Профиль</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>krovlya-sht-trapetsiya</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Штакетник</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Евроштакетник трапеция</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>скошенный верх · ширина 120 мм</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>EURO-Профиль</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>krovlya-sht-pryamoy</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Штакетник</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Штакетник с прямым резом</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>прямой верх · ширина 130 мм</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>EURO-Профиль</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>krovlya-sid-korabelnaya</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Металлосайдинг</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Корабельная доска</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>классика · панель 260 мм</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>EURO-Профиль</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>krovlya-sid-korabelnaya-evro</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Металлосайдинг</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Корабельная доска Евро</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>узкий шов · панель 260 мм</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>EURO-Профиль</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>krovlya-sid-brus-klassik</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Металлосайдинг</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Евробрус Классик</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>под брус · панель 270 мм</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>EURO-Профиль</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>krovlya-sid-brus-riflenyy</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Металлосайдинг</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Евробрус Рифлёный</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>под брус · рифлёная поверхность</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>EURO-Профиль</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>krovlya-sid-sofit</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Металлосайдинг</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Софит перфорированный</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>подшивка свесов · с вентиляцией</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>EURO-Профиль</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I17"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/КАТАЛОГ-ТАБЛИЦА.xlsx
+++ b/КАТАЛОГ-ТАБЛИЦА.xlsx
@@ -3035,7 +3035,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Классик Еврo</t>
+          <t>Классик Евро</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Мокко Вт Еврo</t>
+          <t>Мокко Вт Евро</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Благодать Ретро Ретро</t>
+          <t>Благодать Ретро</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>разное</t>
+          <t>персиковый</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -8019,7 +8019,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Данилово Ретро Ретро</t>
+          <t>Данилово Ретро</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -12634,7 +12634,7 @@
       <c r="N188" s="2" t="inlineStr"/>
       <c r="O188" s="4" t="inlineStr">
         <is>
-          <t>объединён вариант: Светлый кирпич "СЛОНОВАЯ КОСТЬ" Одинарный пустотелый М150 (F50 пустот 37%) 416шт; объединён вариант: СВЕТЛЫЙ УТОЛЩЕННЫЙ ЛИЦЕВОЙ с ФАСКОЙ M175 (F75) 320шт упак. в пленку</t>
+          <t>объединён вариант: Светлый кирпич "СЛОНОВАЯ КОСТЬ" Одинарный пустотелый М150 (F50 пустот 37%) 416шт; объединён вариант: СВЕТЛЫЙ УТОЛЩЕННЫЙ ЛИЦЕВОЙ с ФАСКОЙ М175 (F75) 320шт упак. в пленку</t>
         </is>
       </c>
       <c r="P188" s="2" t="inlineStr">
@@ -14162,7 +14162,7 @@
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>коричневый</t>
+          <t>графит</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
@@ -14745,7 +14745,7 @@
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>руст</t>
+          <t>кора</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
@@ -15033,7 +15033,7 @@
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>руст</t>
+          <t>кора</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
@@ -15106,7 +15106,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>рельефный</t>
+          <t>бриз</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -15948,7 +15948,7 @@
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>антик</t>
+          <t>кора</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
@@ -17187,7 +17187,7 @@
       </c>
       <c r="F254" s="2" t="inlineStr">
         <is>
-          <t>коричневый</t>
+          <t>графит</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
@@ -17730,7 +17730,7 @@
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>руст</t>
+          <t>кора</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
@@ -17797,7 +17797,7 @@
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>руст</t>
+          <t>бриз</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
@@ -18184,7 +18184,7 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>КАМЕНЬ M175 (F75)</t>
+          <t>КАМЕНЬ М175 (F75)</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -19269,7 +19269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -19288,7 +19288,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Собрано автоматически из папки фото · 2026-07-17</t>
+          <t>Собрано автоматически из папки фото · 2026-07-24</t>
         </is>
       </c>
     </row>
@@ -19563,21 +19563,10 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>разное</t>
+          <t>серый</t>
         </is>
       </c>
       <c r="B26" s="9">
-        <f>COUNTIFS(Каталог!F2:F285,"разное",Каталог!C2:C285,"Облицовочный")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>серый</t>
-        </is>
-      </c>
-      <c r="B27" s="9">
         <f>COUNTIFS(Каталог!F2:F285,"серый",Каталог!C2:C285,"Облицовочный")</f>
         <v/>
       </c>
@@ -28419,7 +28408,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>классический профиль · волна 24 мм</t>
+          <t>классический профиль под черепицу</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -28430,7 +28419,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -28505,14 +28494,14 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>заборы и обшивка · волна 8 мм</t>
+          <t>самый ходовой для сплошного забора</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
         <v>40</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -28548,14 +28537,14 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>заборы и стены · волна 10 мм</t>
+          <t>для заборов повыше и обшивки стен</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
         <v>40</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -28591,14 +28580,14 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>универсальный · волна 21 мм</t>
+          <t>симметричный — аккуратен с двух сторон</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
         <v>40</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -28634,14 +28623,14 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>кровля и заборы · волна 20 мм</t>
+          <t>кровельный, с водоотводной канавкой</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
         <v>40</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -28677,14 +28666,14 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>кровля и навесы · волна 35 мм</t>
+          <t>жёсткий — для кровли и навесов</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
         <v>40</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -28720,14 +28709,14 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>несущий · волна 60 мм</t>
+          <t>несущий — пролёты до 6 метров</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
         <v>40</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -28813,7 +28802,7 @@
         <v>12</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -28855,8 +28844,8 @@
       <c r="E12" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F12" s="5" t="n">
-        <v>0</v>
+      <c r="F12" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
@@ -28899,11 +28888,11 @@
         <v>22</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -28941,8 +28930,8 @@
       <c r="E14" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="F14" s="5" t="n">
-        <v>0</v>
+      <c r="F14" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
@@ -28985,11 +28974,11 @@
         <v>22</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -29027,8 +29016,8 @@
       <c r="E16" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="F16" s="5" t="n">
-        <v>0</v>
+      <c r="F16" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
@@ -29070,8 +29059,8 @@
       <c r="E17" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="F17" s="5" t="n">
-        <v>0</v>
+      <c r="F17" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
